--- a/IMU Dataset Trial Posture Sequences.xlsx
+++ b/IMU Dataset Trial Posture Sequences.xlsx
@@ -13,19 +13,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
   <si>
-    <t>Person</t>
-  </si>
-  <si>
-    <t>Sequence</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>height</t>
-  </si>
-  <si>
-    <t>age</t>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Sequence (Postures for trials 1 to 18)</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>Age</t>
   </si>
   <si>
     <t>sub-01</t>
@@ -326,7 +326,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -355,6 +355,7 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font/>
   </fonts>
   <fills count="6">
     <fill>
@@ -388,8 +389,44 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
     <border>
       <left style="thick">
         <color rgb="FF000000"/>
@@ -408,77 +445,81 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -496,6 +537,9 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -505,7 +549,28 @@
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5E5E5"/>
+          <bgColor rgb="FFE5E5E5"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -718,8 +783,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="29.38"/>
-    <col customWidth="1" min="2" max="2" width="28.75"/>
+    <col customWidth="1" min="1" max="1" width="14.63"/>
+    <col customWidth="1" min="2" max="2" width="30.5"/>
     <col customWidth="1" min="8" max="8" width="16.75"/>
   </cols>
   <sheetData>
@@ -754,4838 +819,4851 @@
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>56.0</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>186.0</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>22.0</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="3">
         <v>120.0</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="3">
         <v>172.0</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="3">
         <v>22.0</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>64.0</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>165.0</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>22.0</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
     </row>
     <row r="5" ht="21.0" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>56.0</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>158.0</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>22.0</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="3">
         <v>86.0</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>177.0</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="3">
         <v>21.0</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="5"/>
+      <c r="G6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>48.0</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>162.0</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>22.0</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="10">
+      <c r="F7" s="4"/>
+      <c r="G7" s="8">
         <v>1.0</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="3">
         <v>50.0</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="3">
         <v>164.0</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="3">
         <v>22.0</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="12">
+      <c r="F8" s="5"/>
+      <c r="G8" s="10">
         <v>2.0</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="3">
         <v>47.0</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="3">
         <v>161.0</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="3">
         <v>23.0</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="10">
+      <c r="F9" s="5"/>
+      <c r="G9" s="8">
         <v>3.0</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="3">
         <v>63.0</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="3">
         <v>163.0</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="3">
         <v>22.0</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="12">
+      <c r="F10" s="5"/>
+      <c r="G10" s="10">
         <v>4.0</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>84.0</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>183.0</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>22.0</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="10">
+      <c r="F11" s="4"/>
+      <c r="G11" s="8">
         <v>5.0</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="3">
         <v>65.0</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="3">
         <v>162.0</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="3">
         <v>21.0</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="12">
+      <c r="F12" s="5"/>
+      <c r="G12" s="10">
         <v>6.0</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>58.0</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>152.0</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>22.0</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="3">
         <v>60.0</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="3">
         <v>167.0</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="3">
         <v>22.0</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
         <v>57.0</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>158.0</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="3">
         <v>22.0</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="3">
         <v>57.0</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="3">
         <v>173.0</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="3">
         <v>22.0</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="3">
         <v>51.0</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>153.0</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="3">
         <v>22.0</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="3">
         <v>75.0</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="3">
         <v>172.0</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="3">
         <v>21.0</v>
       </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="13">
         <v>58.0</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="13">
         <v>160.0</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="13">
         <v>21.0</v>
       </c>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="13">
         <v>60.0</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="13">
         <v>162.0</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="13">
         <v>21.0</v>
       </c>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="13">
         <v>65.0</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="13">
         <v>165.0</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="13">
         <v>22.0</v>
       </c>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="18"/>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="13">
         <v>65.0</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="13">
         <v>178.0</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="13">
         <v>24.0</v>
       </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="13">
         <v>70.0</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="13">
         <v>190.0</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="13">
         <v>22.0</v>
       </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="13">
         <v>60.0</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="13">
         <v>158.0</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="13">
         <v>22.0</v>
       </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="13">
         <v>55.0</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="13">
         <v>182.0</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="13">
         <v>24.0</v>
       </c>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="13">
         <v>70.0</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="13">
         <v>180.0</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="13">
         <v>22.0</v>
       </c>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="13">
         <v>75.0</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="13">
         <v>176.0</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="13">
         <v>22.0</v>
       </c>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
-      <c r="M27" s="18"/>
-      <c r="N27" s="18"/>
-      <c r="O27" s="18"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="13">
         <v>51.0</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D28" s="13">
         <v>167.0</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="13">
         <v>21.0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="13">
         <v>90.0</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="13">
         <v>182.0</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="13">
         <v>23.0</v>
       </c>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="13">
         <v>78.0</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D30" s="13">
         <v>181.0</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="13">
         <v>21.0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="13">
         <v>69.0</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="13">
         <v>178.0</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="13">
         <v>22.0</v>
       </c>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="13">
         <v>66.0</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="13">
         <v>170.0</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="13">
         <v>21.0</v>
       </c>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="20"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="13">
         <v>73.0</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="13">
         <v>192.0</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="13">
         <v>21.0</v>
       </c>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="18"/>
-      <c r="N33" s="18"/>
-      <c r="O33" s="18"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="13">
         <v>67.0</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="13">
         <v>160.0</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="13">
         <v>23.0</v>
       </c>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="20"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="17">
+      <c r="C35" s="13">
         <v>81.0</v>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="13">
         <v>167.0</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="13">
         <v>22.0</v>
       </c>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="19">
+      <c r="C36" s="13">
         <v>65.0</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="13">
         <v>172.0</v>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="13">
         <v>22.0</v>
       </c>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="20"/>
-      <c r="N36" s="20"/>
-      <c r="O36" s="20"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="17">
+      <c r="C37" s="13">
         <v>74.0</v>
       </c>
-      <c r="D37" s="17">
+      <c r="D37" s="13">
         <v>183.0</v>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="13">
         <v>23.0</v>
       </c>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
-      <c r="N37" s="18"/>
-      <c r="O37" s="18"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="13">
         <v>55.0</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="13">
         <v>165.0</v>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="13">
         <v>23.0</v>
       </c>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="20"/>
-      <c r="N38" s="20"/>
-      <c r="O38" s="20"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="17">
+      <c r="C39" s="13">
         <v>95.0</v>
       </c>
-      <c r="D39" s="17">
+      <c r="D39" s="13">
         <v>183.0</v>
       </c>
-      <c r="E39" s="17">
+      <c r="E39" s="13">
         <v>22.0</v>
       </c>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
-      <c r="M39" s="18"/>
-      <c r="N39" s="18"/>
-      <c r="O39" s="18"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="14"/>
+      <c r="O39" s="14"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="3">
         <v>75.0</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="3">
         <v>173.0</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="3">
         <v>21.0</v>
       </c>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="19">
+      <c r="C41" s="13">
         <v>78.0</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="13">
         <v>185.0</v>
       </c>
-      <c r="E41" s="19">
+      <c r="E41" s="13">
         <v>22.0</v>
       </c>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="20"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="15"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="19">
+      <c r="C42" s="16">
         <v>54.0</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="16">
         <v>158.0</v>
       </c>
-      <c r="E42" s="19">
+      <c r="E42" s="16">
         <v>22.0</v>
       </c>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="20"/>
-      <c r="O42" s="20"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="15"/>
+      <c r="N42" s="15"/>
+      <c r="O42" s="15"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="19">
+      <c r="C43" s="16">
         <v>50.0</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="16">
         <v>153.0</v>
       </c>
-      <c r="E43" s="19">
+      <c r="E43" s="16">
         <v>22.0</v>
       </c>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="20"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="15"/>
+      <c r="N43" s="15"/>
+      <c r="O43" s="15"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="17">
         <v>57.0</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="17">
         <v>157.0</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="17">
         <v>21.0</v>
       </c>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="3">
         <v>77.0</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="3">
         <v>171.0</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E45" s="3">
         <v>22.0</v>
       </c>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="7"/>
-      <c r="O45" s="7"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="3">
         <v>70.0</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="3">
         <v>175.0</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E46" s="3">
         <v>19.0</v>
       </c>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
-      <c r="O46" s="7"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="17">
         <v>55.0</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="17">
         <v>169.0</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="17">
         <v>22.0</v>
       </c>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
     </row>
     <row r="48">
-      <c r="A48" s="16"/>
+      <c r="A48" s="18"/>
       <c r="B48" s="19"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="20"/>
-      <c r="L48" s="20"/>
-      <c r="M48" s="20"/>
-      <c r="N48" s="20"/>
-      <c r="O48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="15"/>
+      <c r="O48" s="15"/>
     </row>
     <row r="49">
-      <c r="A49" s="16"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="18"/>
-      <c r="K49" s="18"/>
-      <c r="L49" s="18"/>
-      <c r="M49" s="18"/>
-      <c r="N49" s="18"/>
-      <c r="O49" s="18"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="14"/>
     </row>
     <row r="50">
-      <c r="A50" s="16"/>
+      <c r="A50" s="18"/>
       <c r="B50" s="19"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="20"/>
-      <c r="L50" s="20"/>
-      <c r="M50" s="20"/>
-      <c r="N50" s="20"/>
-      <c r="O50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="15"/>
+      <c r="M50" s="15"/>
+      <c r="N50" s="15"/>
+      <c r="O50" s="15"/>
     </row>
     <row r="51">
-      <c r="A51" s="16"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="I51" s="18"/>
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="18"/>
-      <c r="M51" s="18"/>
-      <c r="N51" s="18"/>
-      <c r="O51" s="18"/>
+      <c r="A51" s="18"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="14"/>
+      <c r="M51" s="14"/>
+      <c r="N51" s="14"/>
+      <c r="O51" s="14"/>
     </row>
     <row r="52">
-      <c r="A52" s="16"/>
+      <c r="A52" s="18"/>
       <c r="B52" s="19"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="20"/>
-      <c r="L52" s="20"/>
-      <c r="M52" s="20"/>
-      <c r="N52" s="20"/>
-      <c r="O52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="15"/>
+      <c r="M52" s="15"/>
+      <c r="N52" s="15"/>
+      <c r="O52" s="15"/>
     </row>
     <row r="53">
-      <c r="A53" s="16"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-      <c r="M53" s="18"/>
-      <c r="N53" s="18"/>
-      <c r="O53" s="18"/>
+      <c r="A53" s="18"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="14"/>
+      <c r="M53" s="14"/>
+      <c r="N53" s="14"/>
+      <c r="O53" s="14"/>
     </row>
     <row r="54">
-      <c r="A54" s="16"/>
+      <c r="A54" s="18"/>
       <c r="B54" s="19"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
-      <c r="N54" s="20"/>
-      <c r="O54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="15"/>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
+      <c r="L54" s="15"/>
+      <c r="M54" s="15"/>
+      <c r="N54" s="15"/>
+      <c r="O54" s="15"/>
     </row>
     <row r="55">
-      <c r="A55" s="16"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="18"/>
-      <c r="K55" s="18"/>
-      <c r="L55" s="18"/>
-      <c r="M55" s="18"/>
-      <c r="N55" s="18"/>
-      <c r="O55" s="18"/>
+      <c r="A55" s="18"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="14"/>
+      <c r="N55" s="14"/>
+      <c r="O55" s="14"/>
     </row>
     <row r="56">
-      <c r="A56" s="16"/>
+      <c r="A56" s="18"/>
       <c r="B56" s="19"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-      <c r="K56" s="20"/>
-      <c r="L56" s="20"/>
-      <c r="M56" s="20"/>
-      <c r="N56" s="20"/>
-      <c r="O56" s="20"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="15"/>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="15"/>
+      <c r="M56" s="15"/>
+      <c r="N56" s="15"/>
+      <c r="O56" s="15"/>
     </row>
     <row r="57">
-      <c r="A57" s="16"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="23"/>
-      <c r="E57" s="23"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="18"/>
-      <c r="I57" s="18"/>
-      <c r="J57" s="18"/>
-      <c r="K57" s="18"/>
-      <c r="L57" s="18"/>
-      <c r="M57" s="18"/>
-      <c r="N57" s="18"/>
-      <c r="O57" s="18"/>
+      <c r="A57" s="18"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="14"/>
+      <c r="M57" s="14"/>
+      <c r="N57" s="14"/>
+      <c r="O57" s="14"/>
     </row>
     <row r="58">
-      <c r="A58" s="16"/>
+      <c r="A58" s="18"/>
       <c r="B58" s="19"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="20"/>
-      <c r="K58" s="20"/>
-      <c r="L58" s="20"/>
-      <c r="M58" s="20"/>
-      <c r="N58" s="20"/>
-      <c r="O58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="15"/>
+      <c r="N58" s="15"/>
+      <c r="O58" s="15"/>
     </row>
     <row r="59">
-      <c r="A59" s="16"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
-      <c r="L59" s="18"/>
-      <c r="M59" s="18"/>
-      <c r="N59" s="18"/>
-      <c r="O59" s="18"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+      <c r="M59" s="14"/>
+      <c r="N59" s="14"/>
+      <c r="O59" s="14"/>
     </row>
     <row r="60">
-      <c r="A60" s="16"/>
+      <c r="A60" s="18"/>
       <c r="B60" s="19"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
-      <c r="J60" s="20"/>
-      <c r="K60" s="20"/>
-      <c r="L60" s="20"/>
-      <c r="M60" s="20"/>
-      <c r="N60" s="20"/>
-      <c r="O60" s="20"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="15"/>
     </row>
     <row r="61">
-      <c r="A61" s="16"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-      <c r="H61" s="18"/>
-      <c r="I61" s="18"/>
-      <c r="J61" s="18"/>
-      <c r="K61" s="18"/>
-      <c r="L61" s="18"/>
-      <c r="M61" s="18"/>
-      <c r="N61" s="18"/>
-      <c r="O61" s="18"/>
+      <c r="A61" s="18"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
+      <c r="L61" s="14"/>
+      <c r="M61" s="14"/>
+      <c r="N61" s="14"/>
+      <c r="O61" s="14"/>
     </row>
     <row r="62">
-      <c r="A62" s="16"/>
+      <c r="A62" s="18"/>
       <c r="B62" s="19"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
-      <c r="K62" s="20"/>
-      <c r="L62" s="20"/>
-      <c r="M62" s="20"/>
-      <c r="N62" s="20"/>
-      <c r="O62" s="20"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="15"/>
+      <c r="G62" s="15"/>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="15"/>
+      <c r="M62" s="15"/>
+      <c r="N62" s="15"/>
+      <c r="O62" s="15"/>
     </row>
     <row r="63">
-      <c r="A63" s="16"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="23"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="18"/>
-      <c r="G63" s="18"/>
-      <c r="H63" s="18"/>
-      <c r="I63" s="18"/>
-      <c r="J63" s="18"/>
-      <c r="K63" s="18"/>
-      <c r="L63" s="18"/>
-      <c r="M63" s="18"/>
-      <c r="N63" s="18"/>
-      <c r="O63" s="18"/>
+      <c r="A63" s="18"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="14"/>
+      <c r="L63" s="14"/>
+      <c r="M63" s="14"/>
+      <c r="N63" s="14"/>
+      <c r="O63" s="14"/>
     </row>
     <row r="64">
-      <c r="A64" s="16"/>
+      <c r="A64" s="18"/>
       <c r="B64" s="19"/>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="20"/>
-      <c r="K64" s="20"/>
-      <c r="L64" s="20"/>
-      <c r="M64" s="20"/>
-      <c r="N64" s="20"/>
-      <c r="O64" s="20"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="15"/>
+      <c r="G64" s="15"/>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+      <c r="L64" s="15"/>
+      <c r="M64" s="15"/>
+      <c r="N64" s="15"/>
+      <c r="O64" s="15"/>
     </row>
     <row r="65">
-      <c r="A65" s="16"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="23"/>
-      <c r="D65" s="23"/>
-      <c r="E65" s="23"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
-      <c r="H65" s="18"/>
-      <c r="I65" s="18"/>
-      <c r="J65" s="18"/>
-      <c r="K65" s="18"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="18"/>
-      <c r="N65" s="18"/>
-      <c r="O65" s="18"/>
+      <c r="A65" s="18"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="14"/>
+      <c r="L65" s="14"/>
+      <c r="M65" s="14"/>
+      <c r="N65" s="14"/>
+      <c r="O65" s="14"/>
     </row>
     <row r="66">
-      <c r="A66" s="3"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="24"/>
-      <c r="D66" s="24"/>
-      <c r="E66" s="24"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="5"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
-      <c r="O66" s="5"/>
+      <c r="A66" s="23"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
     </row>
     <row r="67">
-      <c r="A67" s="3"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
-      <c r="K67" s="5"/>
-      <c r="L67" s="5"/>
-      <c r="M67" s="5"/>
-      <c r="N67" s="5"/>
-      <c r="O67" s="5"/>
+      <c r="A67" s="23"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
     </row>
     <row r="68">
-      <c r="A68" s="3"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="25"/>
-      <c r="E68" s="25"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
-      <c r="K68" s="7"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="7"/>
-      <c r="O68" s="7"/>
+      <c r="A68" s="23"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="27"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
     </row>
     <row r="69">
-      <c r="A69" s="3"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
-      <c r="K69" s="5"/>
-      <c r="L69" s="5"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="5"/>
-      <c r="O69" s="5"/>
+      <c r="A69" s="23"/>
+      <c r="B69" s="24"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
     </row>
     <row r="70">
-      <c r="A70" s="3"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="25"/>
-      <c r="D70" s="25"/>
-      <c r="E70" s="25"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
-      <c r="K70" s="7"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
-      <c r="N70" s="7"/>
-      <c r="O70" s="7"/>
+      <c r="A70" s="23"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="27"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
     </row>
     <row r="71">
-      <c r="A71" s="3"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="24"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
-      <c r="L71" s="5"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="5"/>
-      <c r="O71" s="5"/>
+      <c r="A71" s="23"/>
+      <c r="B71" s="24"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
     </row>
     <row r="72">
-      <c r="A72" s="3"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="24"/>
-      <c r="D72" s="24"/>
-      <c r="E72" s="24"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
-      <c r="N72" s="5"/>
-      <c r="O72" s="5"/>
+      <c r="A72" s="23"/>
+      <c r="B72" s="24"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
     </row>
     <row r="73">
-      <c r="A73" s="3"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="25"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="7"/>
-      <c r="J73" s="7"/>
-      <c r="K73" s="7"/>
-      <c r="L73" s="7"/>
-      <c r="M73" s="7"/>
-      <c r="N73" s="7"/>
-      <c r="O73" s="7"/>
+      <c r="A73" s="23"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="27"/>
+      <c r="D73" s="27"/>
+      <c r="E73" s="27"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
     </row>
     <row r="74">
-      <c r="A74" s="3"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="24"/>
-      <c r="D74" s="24"/>
-      <c r="E74" s="24"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
-      <c r="N74" s="5"/>
-      <c r="O74" s="5"/>
+      <c r="A74" s="23"/>
+      <c r="B74" s="24"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
     </row>
     <row r="75">
-      <c r="A75" s="3"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="7"/>
-      <c r="K75" s="7"/>
-      <c r="L75" s="7"/>
-      <c r="M75" s="7"/>
-      <c r="N75" s="7"/>
-      <c r="O75" s="7"/>
+      <c r="A75" s="23"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="27"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="27"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
     </row>
     <row r="76">
-      <c r="A76" s="3"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="25"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="7"/>
-      <c r="O76" s="7"/>
+      <c r="A76" s="23"/>
+      <c r="B76" s="26"/>
+      <c r="C76" s="27"/>
+      <c r="D76" s="27"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5"/>
+      <c r="L76" s="5"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
     </row>
     <row r="77">
-      <c r="A77" s="3"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="24"/>
-      <c r="D77" s="24"/>
-      <c r="E77" s="24"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
-      <c r="I77" s="5"/>
-      <c r="J77" s="5"/>
-      <c r="K77" s="5"/>
-      <c r="L77" s="5"/>
-      <c r="M77" s="5"/>
-      <c r="N77" s="5"/>
-      <c r="O77" s="5"/>
+      <c r="A77" s="23"/>
+      <c r="B77" s="24"/>
+      <c r="C77" s="25"/>
+      <c r="D77" s="25"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
     </row>
     <row r="78">
-      <c r="A78" s="3"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="25"/>
-      <c r="E78" s="25"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
-      <c r="I78" s="7"/>
-      <c r="J78" s="7"/>
-      <c r="K78" s="7"/>
-      <c r="L78" s="7"/>
-      <c r="M78" s="7"/>
-      <c r="N78" s="7"/>
-      <c r="O78" s="7"/>
+      <c r="A78" s="23"/>
+      <c r="B78" s="26"/>
+      <c r="C78" s="27"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="27"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="5"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
     </row>
     <row r="79">
-      <c r="A79" s="3"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="24"/>
-      <c r="D79" s="24"/>
-      <c r="E79" s="24"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
-      <c r="I79" s="5"/>
-      <c r="J79" s="5"/>
-      <c r="K79" s="5"/>
-      <c r="L79" s="5"/>
-      <c r="M79" s="5"/>
-      <c r="N79" s="5"/>
-      <c r="O79" s="5"/>
+      <c r="A79" s="23"/>
+      <c r="B79" s="24"/>
+      <c r="C79" s="25"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="25"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
     </row>
     <row r="80">
-      <c r="A80" s="16"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="7"/>
-      <c r="K80" s="7"/>
-      <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
-      <c r="N80" s="7"/>
-      <c r="O80" s="7"/>
+      <c r="A80" s="18"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="27"/>
+      <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="5"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
     </row>
     <row r="81">
-      <c r="A81" s="26"/>
-      <c r="B81" s="27"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
-      <c r="I81" s="5"/>
-      <c r="J81" s="5"/>
-      <c r="K81" s="5"/>
-      <c r="L81" s="5"/>
-      <c r="M81" s="5"/>
-      <c r="N81" s="5"/>
-      <c r="O81" s="5"/>
+      <c r="A81" s="28"/>
+      <c r="B81" s="29"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
     </row>
     <row r="82">
-      <c r="A82" s="26"/>
-      <c r="B82" s="28"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="7"/>
-      <c r="H82" s="7"/>
-      <c r="I82" s="7"/>
-      <c r="J82" s="7"/>
-      <c r="K82" s="7"/>
-      <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
-      <c r="N82" s="7"/>
-      <c r="O82" s="7"/>
+      <c r="A82" s="28"/>
+      <c r="B82" s="30"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="5"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5"/>
     </row>
     <row r="83">
-      <c r="A83" s="26"/>
-      <c r="B83" s="27"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-      <c r="G83" s="5"/>
-      <c r="H83" s="5"/>
-      <c r="I83" s="5"/>
-      <c r="J83" s="5"/>
-      <c r="K83" s="5"/>
-      <c r="L83" s="5"/>
-      <c r="M83" s="5"/>
-      <c r="N83" s="5"/>
-      <c r="O83" s="5"/>
+      <c r="A83" s="28"/>
+      <c r="B83" s="29"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
+      <c r="O83" s="4"/>
     </row>
     <row r="84" ht="31.5" customHeight="1">
-      <c r="A84" s="29"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="24"/>
-      <c r="D84" s="24"/>
-      <c r="E84" s="24"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="5"/>
-      <c r="H84" s="5"/>
-      <c r="I84" s="5"/>
-      <c r="J84" s="5"/>
-      <c r="K84" s="5"/>
-      <c r="L84" s="5"/>
-      <c r="M84" s="5"/>
-      <c r="N84" s="5"/>
-      <c r="O84" s="5"/>
+      <c r="A84" s="31"/>
+      <c r="B84" s="24"/>
+      <c r="C84" s="25"/>
+      <c r="D84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
     </row>
     <row r="85">
-      <c r="A85" s="3"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="25"/>
-      <c r="D85" s="25"/>
-      <c r="E85" s="25"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-      <c r="I85" s="7"/>
-      <c r="J85" s="7"/>
-      <c r="K85" s="7"/>
-      <c r="L85" s="7"/>
-      <c r="M85" s="7"/>
-      <c r="N85" s="7"/>
-      <c r="O85" s="7"/>
+      <c r="A85" s="23"/>
+      <c r="B85" s="26"/>
+      <c r="C85" s="27"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="5"/>
+      <c r="K85" s="5"/>
+      <c r="L85" s="5"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5"/>
     </row>
     <row r="86">
-      <c r="A86" s="16"/>
+      <c r="A86" s="18"/>
       <c r="B86" s="19"/>
-      <c r="C86" s="22"/>
-      <c r="D86" s="22"/>
-      <c r="E86" s="22"/>
-      <c r="F86" s="20"/>
-      <c r="G86" s="20"/>
-      <c r="H86" s="20"/>
-      <c r="I86" s="20"/>
-      <c r="J86" s="20"/>
-      <c r="K86" s="20"/>
-      <c r="L86" s="20"/>
-      <c r="M86" s="20"/>
-      <c r="N86" s="20"/>
-      <c r="O86" s="20"/>
+      <c r="C86" s="20"/>
+      <c r="D86" s="20"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="15"/>
+      <c r="G86" s="15"/>
+      <c r="H86" s="15"/>
+      <c r="I86" s="15"/>
+      <c r="J86" s="15"/>
+      <c r="K86" s="15"/>
+      <c r="L86" s="15"/>
+      <c r="M86" s="15"/>
+      <c r="N86" s="15"/>
+      <c r="O86" s="15"/>
     </row>
     <row r="87">
-      <c r="A87" s="16"/>
-      <c r="B87" s="17"/>
-      <c r="C87" s="23"/>
-      <c r="D87" s="23"/>
-      <c r="E87" s="23"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18"/>
-      <c r="H87" s="18"/>
-      <c r="I87" s="18"/>
-      <c r="J87" s="18"/>
-      <c r="K87" s="18"/>
-      <c r="L87" s="18"/>
-      <c r="M87" s="18"/>
-      <c r="N87" s="18"/>
-      <c r="O87" s="18"/>
+      <c r="A87" s="18"/>
+      <c r="B87" s="21"/>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+      <c r="K87" s="14"/>
+      <c r="L87" s="14"/>
+      <c r="M87" s="14"/>
+      <c r="N87" s="14"/>
+      <c r="O87" s="14"/>
     </row>
     <row r="88">
-      <c r="A88" s="16"/>
+      <c r="A88" s="18"/>
       <c r="B88" s="19"/>
-      <c r="C88" s="22"/>
-      <c r="D88" s="22"/>
-      <c r="E88" s="22"/>
-      <c r="F88" s="20"/>
-      <c r="G88" s="20"/>
-      <c r="H88" s="20"/>
-      <c r="I88" s="20"/>
-      <c r="J88" s="20"/>
-      <c r="K88" s="20"/>
-      <c r="L88" s="20"/>
-      <c r="M88" s="20"/>
-      <c r="N88" s="20"/>
-      <c r="O88" s="20"/>
+      <c r="C88" s="20"/>
+      <c r="D88" s="20"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="15"/>
+      <c r="G88" s="15"/>
+      <c r="H88" s="15"/>
+      <c r="I88" s="15"/>
+      <c r="J88" s="15"/>
+      <c r="K88" s="15"/>
+      <c r="L88" s="15"/>
+      <c r="M88" s="15"/>
+      <c r="N88" s="15"/>
+      <c r="O88" s="15"/>
     </row>
     <row r="89">
-      <c r="A89" s="16"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="23"/>
-      <c r="D89" s="23"/>
-      <c r="E89" s="23"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="18"/>
-      <c r="H89" s="18"/>
-      <c r="I89" s="18"/>
-      <c r="J89" s="18"/>
-      <c r="K89" s="18"/>
-      <c r="L89" s="18"/>
-      <c r="M89" s="18"/>
-      <c r="N89" s="18"/>
-      <c r="O89" s="18"/>
+      <c r="A89" s="18"/>
+      <c r="B89" s="21"/>
+      <c r="C89" s="22"/>
+      <c r="D89" s="22"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="14"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="14"/>
+      <c r="K89" s="14"/>
+      <c r="L89" s="14"/>
+      <c r="M89" s="14"/>
+      <c r="N89" s="14"/>
+      <c r="O89" s="14"/>
     </row>
     <row r="90">
-      <c r="A90" s="16"/>
+      <c r="A90" s="18"/>
       <c r="B90" s="19"/>
-      <c r="C90" s="22"/>
-      <c r="D90" s="22"/>
-      <c r="E90" s="22"/>
-      <c r="F90" s="20"/>
-      <c r="G90" s="20"/>
-      <c r="H90" s="20"/>
-      <c r="I90" s="20"/>
-      <c r="J90" s="20"/>
-      <c r="K90" s="20"/>
-      <c r="L90" s="20"/>
-      <c r="M90" s="20"/>
-      <c r="N90" s="20"/>
-      <c r="O90" s="20"/>
+      <c r="C90" s="20"/>
+      <c r="D90" s="20"/>
+      <c r="E90" s="20"/>
+      <c r="F90" s="15"/>
+      <c r="G90" s="15"/>
+      <c r="H90" s="15"/>
+      <c r="I90" s="15"/>
+      <c r="J90" s="15"/>
+      <c r="K90" s="15"/>
+      <c r="L90" s="15"/>
+      <c r="M90" s="15"/>
+      <c r="N90" s="15"/>
+      <c r="O90" s="15"/>
     </row>
     <row r="91">
-      <c r="A91" s="16"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="23"/>
-      <c r="D91" s="23"/>
-      <c r="E91" s="23"/>
-      <c r="F91" s="18"/>
-      <c r="G91" s="18"/>
-      <c r="H91" s="18"/>
-      <c r="I91" s="18"/>
-      <c r="J91" s="18"/>
-      <c r="K91" s="18"/>
-      <c r="L91" s="18"/>
-      <c r="M91" s="18"/>
-      <c r="N91" s="18"/>
-      <c r="O91" s="18"/>
+      <c r="A91" s="18"/>
+      <c r="B91" s="21"/>
+      <c r="C91" s="22"/>
+      <c r="D91" s="22"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14"/>
+      <c r="K91" s="14"/>
+      <c r="L91" s="14"/>
+      <c r="M91" s="14"/>
+      <c r="N91" s="14"/>
+      <c r="O91" s="14"/>
     </row>
     <row r="92">
-      <c r="A92" s="16"/>
-      <c r="B92" s="21"/>
-      <c r="C92" s="30"/>
-      <c r="D92" s="30"/>
-      <c r="E92" s="30"/>
+      <c r="A92" s="18"/>
+      <c r="B92" s="32"/>
+      <c r="C92" s="33"/>
+      <c r="D92" s="33"/>
+      <c r="E92" s="33"/>
     </row>
     <row r="93">
-      <c r="A93" s="16"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="23"/>
-      <c r="D93" s="23"/>
-      <c r="E93" s="23"/>
-      <c r="F93" s="18"/>
-      <c r="G93" s="18"/>
-      <c r="H93" s="18"/>
-      <c r="I93" s="18"/>
-      <c r="J93" s="18"/>
-      <c r="K93" s="18"/>
-      <c r="L93" s="18"/>
-      <c r="M93" s="18"/>
-      <c r="N93" s="18"/>
-      <c r="O93" s="18"/>
+      <c r="A93" s="18"/>
+      <c r="B93" s="21"/>
+      <c r="C93" s="22"/>
+      <c r="D93" s="22"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="H93" s="14"/>
+      <c r="I93" s="14"/>
+      <c r="J93" s="14"/>
+      <c r="K93" s="14"/>
+      <c r="L93" s="14"/>
+      <c r="M93" s="14"/>
+      <c r="N93" s="14"/>
+      <c r="O93" s="14"/>
     </row>
     <row r="94">
-      <c r="A94" s="16"/>
-      <c r="B94" s="21"/>
-      <c r="C94" s="30"/>
-      <c r="D94" s="30"/>
-      <c r="E94" s="30"/>
+      <c r="A94" s="18"/>
+      <c r="B94" s="32"/>
+      <c r="C94" s="33"/>
+      <c r="D94" s="33"/>
+      <c r="E94" s="33"/>
     </row>
     <row r="95">
-      <c r="A95" s="16"/>
-      <c r="B95" s="17"/>
-      <c r="C95" s="23"/>
-      <c r="D95" s="23"/>
-      <c r="E95" s="23"/>
-      <c r="F95" s="18"/>
-      <c r="G95" s="18"/>
-      <c r="H95" s="18"/>
-      <c r="I95" s="18"/>
-      <c r="J95" s="18"/>
-      <c r="K95" s="18"/>
-      <c r="L95" s="18"/>
-      <c r="M95" s="18"/>
-      <c r="N95" s="18"/>
-      <c r="O95" s="18"/>
+      <c r="A95" s="18"/>
+      <c r="B95" s="21"/>
+      <c r="C95" s="22"/>
+      <c r="D95" s="22"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="14"/>
+      <c r="G95" s="14"/>
+      <c r="H95" s="14"/>
+      <c r="I95" s="14"/>
+      <c r="J95" s="14"/>
+      <c r="K95" s="14"/>
+      <c r="L95" s="14"/>
+      <c r="M95" s="14"/>
+      <c r="N95" s="14"/>
+      <c r="O95" s="14"/>
     </row>
     <row r="96">
-      <c r="A96" s="16"/>
-      <c r="B96" s="21"/>
-      <c r="C96" s="30"/>
-      <c r="D96" s="30"/>
-      <c r="E96" s="30"/>
+      <c r="A96" s="18"/>
+      <c r="B96" s="32"/>
+      <c r="C96" s="33"/>
+      <c r="D96" s="33"/>
+      <c r="E96" s="33"/>
     </row>
     <row r="97">
-      <c r="A97" s="16"/>
-      <c r="B97" s="17"/>
-      <c r="C97" s="23"/>
-      <c r="D97" s="23"/>
-      <c r="E97" s="23"/>
-      <c r="F97" s="18"/>
-      <c r="G97" s="18"/>
-      <c r="H97" s="18"/>
-      <c r="I97" s="18"/>
-      <c r="J97" s="18"/>
-      <c r="K97" s="18"/>
-      <c r="L97" s="18"/>
-      <c r="M97" s="18"/>
-      <c r="N97" s="18"/>
-      <c r="O97" s="18"/>
+      <c r="A97" s="18"/>
+      <c r="B97" s="21"/>
+      <c r="C97" s="22"/>
+      <c r="D97" s="22"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
+      <c r="J97" s="14"/>
+      <c r="K97" s="14"/>
+      <c r="L97" s="14"/>
+      <c r="M97" s="14"/>
+      <c r="N97" s="14"/>
+      <c r="O97" s="14"/>
     </row>
     <row r="98">
-      <c r="A98" s="16"/>
-      <c r="B98" s="21"/>
-      <c r="C98" s="30"/>
-      <c r="D98" s="30"/>
-      <c r="E98" s="30"/>
+      <c r="A98" s="18"/>
+      <c r="B98" s="32"/>
+      <c r="C98" s="33"/>
+      <c r="D98" s="33"/>
+      <c r="E98" s="33"/>
     </row>
     <row r="99">
-      <c r="A99" s="16"/>
-      <c r="B99" s="17"/>
-      <c r="C99" s="23"/>
-      <c r="D99" s="23"/>
-      <c r="E99" s="23"/>
-      <c r="F99" s="18"/>
-      <c r="G99" s="18"/>
-      <c r="H99" s="18"/>
-      <c r="I99" s="18"/>
-      <c r="J99" s="18"/>
-      <c r="K99" s="18"/>
-      <c r="L99" s="18"/>
-      <c r="M99" s="18"/>
-      <c r="N99" s="18"/>
-      <c r="O99" s="18"/>
+      <c r="A99" s="18"/>
+      <c r="B99" s="21"/>
+      <c r="C99" s="22"/>
+      <c r="D99" s="22"/>
+      <c r="E99" s="22"/>
+      <c r="F99" s="14"/>
+      <c r="G99" s="14"/>
+      <c r="H99" s="14"/>
+      <c r="I99" s="14"/>
+      <c r="J99" s="14"/>
+      <c r="K99" s="14"/>
+      <c r="L99" s="14"/>
+      <c r="M99" s="14"/>
+      <c r="N99" s="14"/>
+      <c r="O99" s="14"/>
     </row>
     <row r="100">
-      <c r="A100" s="16"/>
-      <c r="B100" s="21"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
+      <c r="A100" s="18"/>
+      <c r="B100" s="32"/>
+      <c r="C100" s="33"/>
+      <c r="D100" s="33"/>
+      <c r="E100" s="33"/>
     </row>
     <row r="101">
-      <c r="A101" s="16"/>
-      <c r="B101" s="17"/>
-      <c r="C101" s="23"/>
-      <c r="D101" s="23"/>
-      <c r="E101" s="23"/>
-      <c r="F101" s="18"/>
-      <c r="G101" s="18"/>
-      <c r="H101" s="18"/>
-      <c r="I101" s="18"/>
-      <c r="J101" s="18"/>
-      <c r="K101" s="18"/>
-      <c r="L101" s="18"/>
-      <c r="M101" s="18"/>
-      <c r="N101" s="18"/>
-      <c r="O101" s="18"/>
+      <c r="A101" s="18"/>
+      <c r="B101" s="21"/>
+      <c r="C101" s="22"/>
+      <c r="D101" s="22"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="14"/>
+      <c r="G101" s="14"/>
+      <c r="H101" s="14"/>
+      <c r="I101" s="14"/>
+      <c r="J101" s="14"/>
+      <c r="K101" s="14"/>
+      <c r="L101" s="14"/>
+      <c r="M101" s="14"/>
+      <c r="N101" s="14"/>
+      <c r="O101" s="14"/>
     </row>
     <row r="102">
-      <c r="A102" s="16"/>
-      <c r="B102" s="21"/>
-      <c r="C102" s="30"/>
-      <c r="D102" s="30"/>
-      <c r="E102" s="30"/>
+      <c r="A102" s="18"/>
+      <c r="B102" s="32"/>
+      <c r="C102" s="33"/>
+      <c r="D102" s="33"/>
+      <c r="E102" s="33"/>
     </row>
     <row r="103">
-      <c r="A103" s="16"/>
-      <c r="B103" s="17"/>
-      <c r="C103" s="23"/>
-      <c r="D103" s="23"/>
-      <c r="E103" s="23"/>
-      <c r="F103" s="18"/>
-      <c r="G103" s="18"/>
-      <c r="H103" s="18"/>
-      <c r="I103" s="18"/>
-      <c r="J103" s="18"/>
-      <c r="K103" s="18"/>
-      <c r="L103" s="18"/>
-      <c r="M103" s="18"/>
-      <c r="N103" s="18"/>
-      <c r="O103" s="18"/>
+      <c r="A103" s="18"/>
+      <c r="B103" s="21"/>
+      <c r="C103" s="22"/>
+      <c r="D103" s="22"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="14"/>
+      <c r="G103" s="14"/>
+      <c r="H103" s="14"/>
+      <c r="I103" s="14"/>
+      <c r="J103" s="14"/>
+      <c r="K103" s="14"/>
+      <c r="L103" s="14"/>
+      <c r="M103" s="14"/>
+      <c r="N103" s="14"/>
+      <c r="O103" s="14"/>
     </row>
     <row r="104">
-      <c r="A104" s="16"/>
-      <c r="B104" s="21"/>
-      <c r="C104" s="30"/>
-      <c r="D104" s="30"/>
-      <c r="E104" s="30"/>
+      <c r="A104" s="18"/>
+      <c r="B104" s="32"/>
+      <c r="C104" s="33"/>
+      <c r="D104" s="33"/>
+      <c r="E104" s="33"/>
     </row>
     <row r="105">
-      <c r="A105" s="31"/>
+      <c r="A105" s="34"/>
     </row>
     <row r="106">
-      <c r="A106" s="31"/>
+      <c r="A106" s="34"/>
     </row>
     <row r="107">
-      <c r="A107" s="31"/>
+      <c r="A107" s="34"/>
     </row>
     <row r="108">
-      <c r="A108" s="31"/>
+      <c r="A108" s="34"/>
     </row>
     <row r="109">
-      <c r="A109" s="31"/>
+      <c r="A109" s="34"/>
     </row>
     <row r="110">
-      <c r="A110" s="31"/>
+      <c r="A110" s="34"/>
     </row>
     <row r="111">
-      <c r="A111" s="31"/>
+      <c r="A111" s="34"/>
     </row>
     <row r="112">
-      <c r="A112" s="31"/>
+      <c r="A112" s="34"/>
     </row>
     <row r="113">
-      <c r="A113" s="31"/>
+      <c r="A113" s="34"/>
     </row>
     <row r="114">
-      <c r="A114" s="31"/>
+      <c r="A114" s="34"/>
     </row>
     <row r="115">
-      <c r="A115" s="31"/>
+      <c r="A115" s="34"/>
     </row>
     <row r="116">
-      <c r="A116" s="31"/>
+      <c r="A116" s="34"/>
     </row>
     <row r="117">
-      <c r="A117" s="31"/>
+      <c r="A117" s="34"/>
     </row>
     <row r="118">
-      <c r="A118" s="31"/>
+      <c r="A118" s="34"/>
     </row>
     <row r="119">
-      <c r="A119" s="31"/>
+      <c r="A119" s="34"/>
     </row>
     <row r="120">
-      <c r="A120" s="31"/>
+      <c r="A120" s="34"/>
     </row>
     <row r="121">
-      <c r="A121" s="31"/>
+      <c r="A121" s="34"/>
     </row>
     <row r="122">
-      <c r="A122" s="31"/>
+      <c r="A122" s="34"/>
     </row>
     <row r="123">
-      <c r="A123" s="31"/>
+      <c r="A123" s="34"/>
     </row>
     <row r="124">
-      <c r="A124" s="31"/>
+      <c r="A124" s="34"/>
     </row>
     <row r="125">
-      <c r="A125" s="31"/>
+      <c r="A125" s="34"/>
     </row>
     <row r="126">
-      <c r="A126" s="31"/>
+      <c r="A126" s="34"/>
     </row>
     <row r="127">
-      <c r="A127" s="31"/>
+      <c r="A127" s="34"/>
     </row>
     <row r="128">
-      <c r="A128" s="31"/>
+      <c r="A128" s="34"/>
     </row>
     <row r="129">
-      <c r="A129" s="31"/>
+      <c r="A129" s="34"/>
     </row>
     <row r="130">
-      <c r="A130" s="31"/>
+      <c r="A130" s="34"/>
     </row>
     <row r="131">
-      <c r="A131" s="31"/>
+      <c r="A131" s="34"/>
     </row>
     <row r="132">
-      <c r="A132" s="31"/>
+      <c r="A132" s="34"/>
     </row>
     <row r="133">
-      <c r="A133" s="31"/>
+      <c r="A133" s="34"/>
     </row>
     <row r="134">
-      <c r="A134" s="31"/>
+      <c r="A134" s="34"/>
     </row>
     <row r="135">
-      <c r="A135" s="31"/>
+      <c r="A135" s="34"/>
     </row>
     <row r="136">
-      <c r="A136" s="31"/>
+      <c r="A136" s="34"/>
     </row>
     <row r="137">
-      <c r="A137" s="31"/>
+      <c r="A137" s="34"/>
     </row>
     <row r="138">
-      <c r="A138" s="31"/>
+      <c r="A138" s="34"/>
     </row>
     <row r="139">
-      <c r="A139" s="31"/>
+      <c r="A139" s="34"/>
     </row>
     <row r="140">
-      <c r="A140" s="31"/>
+      <c r="A140" s="34"/>
     </row>
     <row r="141">
-      <c r="A141" s="31"/>
+      <c r="A141" s="34"/>
     </row>
     <row r="142">
-      <c r="A142" s="31"/>
+      <c r="A142" s="34"/>
     </row>
     <row r="143">
-      <c r="A143" s="31"/>
+      <c r="A143" s="34"/>
     </row>
     <row r="144">
-      <c r="A144" s="31"/>
+      <c r="A144" s="34"/>
     </row>
     <row r="145">
-      <c r="A145" s="31"/>
+      <c r="A145" s="34"/>
     </row>
     <row r="146">
-      <c r="A146" s="31"/>
+      <c r="A146" s="34"/>
     </row>
     <row r="147">
-      <c r="A147" s="31"/>
+      <c r="A147" s="34"/>
     </row>
     <row r="148">
-      <c r="A148" s="31"/>
+      <c r="A148" s="34"/>
     </row>
     <row r="149">
-      <c r="A149" s="31"/>
+      <c r="A149" s="34"/>
     </row>
     <row r="150">
-      <c r="A150" s="31"/>
+      <c r="A150" s="34"/>
     </row>
     <row r="151">
-      <c r="A151" s="31"/>
+      <c r="A151" s="34"/>
     </row>
     <row r="152">
-      <c r="A152" s="31"/>
+      <c r="A152" s="34"/>
     </row>
     <row r="153">
-      <c r="A153" s="31"/>
+      <c r="A153" s="34"/>
     </row>
     <row r="154">
-      <c r="A154" s="31"/>
+      <c r="A154" s="34"/>
     </row>
     <row r="155">
-      <c r="A155" s="31"/>
+      <c r="A155" s="34"/>
     </row>
     <row r="156">
-      <c r="A156" s="31"/>
+      <c r="A156" s="34"/>
     </row>
     <row r="157">
-      <c r="A157" s="31"/>
+      <c r="A157" s="34"/>
     </row>
     <row r="158">
-      <c r="A158" s="31"/>
+      <c r="A158" s="34"/>
     </row>
     <row r="159">
-      <c r="A159" s="31"/>
+      <c r="A159" s="34"/>
     </row>
     <row r="160">
-      <c r="A160" s="31"/>
+      <c r="A160" s="34"/>
     </row>
     <row r="161">
-      <c r="A161" s="31"/>
+      <c r="A161" s="34"/>
     </row>
     <row r="162">
-      <c r="A162" s="31"/>
+      <c r="A162" s="34"/>
     </row>
     <row r="163">
-      <c r="A163" s="31"/>
+      <c r="A163" s="34"/>
     </row>
     <row r="164">
-      <c r="A164" s="31"/>
+      <c r="A164" s="34"/>
     </row>
     <row r="165">
-      <c r="A165" s="31"/>
+      <c r="A165" s="34"/>
     </row>
     <row r="166">
-      <c r="A166" s="31"/>
+      <c r="A166" s="34"/>
     </row>
     <row r="167">
-      <c r="A167" s="31"/>
+      <c r="A167" s="34"/>
     </row>
     <row r="168">
-      <c r="A168" s="31"/>
+      <c r="A168" s="34"/>
     </row>
     <row r="169">
-      <c r="A169" s="31"/>
+      <c r="A169" s="34"/>
     </row>
     <row r="170">
-      <c r="A170" s="31"/>
+      <c r="A170" s="34"/>
     </row>
     <row r="171">
-      <c r="A171" s="31"/>
+      <c r="A171" s="34"/>
     </row>
     <row r="172">
-      <c r="A172" s="31"/>
+      <c r="A172" s="34"/>
     </row>
     <row r="173">
-      <c r="A173" s="31"/>
+      <c r="A173" s="34"/>
     </row>
     <row r="174">
-      <c r="A174" s="31"/>
+      <c r="A174" s="34"/>
     </row>
     <row r="175">
-      <c r="A175" s="31"/>
+      <c r="A175" s="34"/>
     </row>
     <row r="176">
-      <c r="A176" s="31"/>
+      <c r="A176" s="34"/>
     </row>
     <row r="177">
-      <c r="A177" s="31"/>
+      <c r="A177" s="34"/>
     </row>
     <row r="178">
-      <c r="A178" s="31"/>
+      <c r="A178" s="34"/>
     </row>
     <row r="179">
-      <c r="A179" s="31"/>
+      <c r="A179" s="34"/>
     </row>
     <row r="180">
-      <c r="A180" s="31"/>
+      <c r="A180" s="34"/>
     </row>
     <row r="181">
-      <c r="A181" s="31"/>
+      <c r="A181" s="34"/>
     </row>
     <row r="182">
-      <c r="A182" s="31"/>
+      <c r="A182" s="34"/>
     </row>
     <row r="183">
-      <c r="A183" s="31"/>
+      <c r="A183" s="34"/>
     </row>
     <row r="184">
-      <c r="A184" s="31"/>
+      <c r="A184" s="34"/>
     </row>
     <row r="185">
-      <c r="A185" s="31"/>
+      <c r="A185" s="34"/>
     </row>
     <row r="186">
-      <c r="A186" s="31"/>
+      <c r="A186" s="34"/>
     </row>
     <row r="187">
-      <c r="A187" s="31"/>
+      <c r="A187" s="34"/>
     </row>
     <row r="188">
-      <c r="A188" s="31"/>
+      <c r="A188" s="34"/>
     </row>
     <row r="189">
-      <c r="A189" s="31"/>
+      <c r="A189" s="34"/>
     </row>
     <row r="190">
-      <c r="A190" s="31"/>
+      <c r="A190" s="34"/>
     </row>
     <row r="191">
-      <c r="A191" s="31"/>
+      <c r="A191" s="34"/>
     </row>
     <row r="192">
-      <c r="A192" s="31"/>
+      <c r="A192" s="34"/>
     </row>
     <row r="193">
-      <c r="A193" s="31"/>
+      <c r="A193" s="34"/>
     </row>
     <row r="194">
-      <c r="A194" s="31"/>
+      <c r="A194" s="34"/>
     </row>
     <row r="195">
-      <c r="A195" s="31"/>
+      <c r="A195" s="34"/>
     </row>
     <row r="196">
-      <c r="A196" s="31"/>
+      <c r="A196" s="34"/>
     </row>
     <row r="197">
-      <c r="A197" s="31"/>
+      <c r="A197" s="34"/>
     </row>
     <row r="198">
-      <c r="A198" s="31"/>
+      <c r="A198" s="34"/>
     </row>
     <row r="199">
-      <c r="A199" s="31"/>
+      <c r="A199" s="34"/>
     </row>
     <row r="200">
-      <c r="A200" s="31"/>
+      <c r="A200" s="34"/>
     </row>
     <row r="201">
-      <c r="A201" s="31"/>
+      <c r="A201" s="34"/>
     </row>
     <row r="202">
-      <c r="A202" s="31"/>
+      <c r="A202" s="34"/>
     </row>
     <row r="203">
-      <c r="A203" s="31"/>
+      <c r="A203" s="34"/>
     </row>
     <row r="204">
-      <c r="A204" s="31"/>
+      <c r="A204" s="34"/>
     </row>
     <row r="205">
-      <c r="A205" s="31"/>
+      <c r="A205" s="34"/>
     </row>
     <row r="206">
-      <c r="A206" s="31"/>
+      <c r="A206" s="34"/>
     </row>
     <row r="207">
-      <c r="A207" s="31"/>
+      <c r="A207" s="34"/>
     </row>
     <row r="208">
-      <c r="A208" s="31"/>
+      <c r="A208" s="34"/>
     </row>
     <row r="209">
-      <c r="A209" s="31"/>
+      <c r="A209" s="34"/>
     </row>
     <row r="210">
-      <c r="A210" s="31"/>
+      <c r="A210" s="34"/>
     </row>
     <row r="211">
-      <c r="A211" s="31"/>
+      <c r="A211" s="34"/>
     </row>
     <row r="212">
-      <c r="A212" s="31"/>
+      <c r="A212" s="34"/>
     </row>
     <row r="213">
-      <c r="A213" s="31"/>
+      <c r="A213" s="34"/>
     </row>
     <row r="214">
-      <c r="A214" s="31"/>
+      <c r="A214" s="34"/>
     </row>
     <row r="215">
-      <c r="A215" s="31"/>
+      <c r="A215" s="34"/>
     </row>
     <row r="216">
-      <c r="A216" s="31"/>
+      <c r="A216" s="34"/>
     </row>
     <row r="217">
-      <c r="A217" s="31"/>
+      <c r="A217" s="34"/>
     </row>
     <row r="218">
-      <c r="A218" s="31"/>
+      <c r="A218" s="34"/>
     </row>
     <row r="219">
-      <c r="A219" s="31"/>
+      <c r="A219" s="34"/>
     </row>
     <row r="220">
-      <c r="A220" s="31"/>
+      <c r="A220" s="34"/>
     </row>
     <row r="221">
-      <c r="A221" s="31"/>
+      <c r="A221" s="34"/>
     </row>
     <row r="222">
-      <c r="A222" s="31"/>
+      <c r="A222" s="34"/>
     </row>
     <row r="223">
-      <c r="A223" s="31"/>
+      <c r="A223" s="34"/>
     </row>
     <row r="224">
-      <c r="A224" s="31"/>
+      <c r="A224" s="34"/>
     </row>
     <row r="225">
-      <c r="A225" s="31"/>
+      <c r="A225" s="34"/>
     </row>
     <row r="226">
-      <c r="A226" s="31"/>
+      <c r="A226" s="34"/>
     </row>
     <row r="227">
-      <c r="A227" s="31"/>
+      <c r="A227" s="34"/>
     </row>
     <row r="228">
-      <c r="A228" s="31"/>
+      <c r="A228" s="34"/>
     </row>
     <row r="229">
-      <c r="A229" s="31"/>
+      <c r="A229" s="34"/>
     </row>
     <row r="230">
-      <c r="A230" s="31"/>
+      <c r="A230" s="34"/>
     </row>
     <row r="231">
-      <c r="A231" s="31"/>
+      <c r="A231" s="34"/>
     </row>
     <row r="232">
-      <c r="A232" s="31"/>
+      <c r="A232" s="34"/>
     </row>
     <row r="233">
-      <c r="A233" s="31"/>
+      <c r="A233" s="34"/>
     </row>
     <row r="234">
-      <c r="A234" s="31"/>
+      <c r="A234" s="34"/>
     </row>
     <row r="235">
-      <c r="A235" s="31"/>
+      <c r="A235" s="34"/>
     </row>
     <row r="236">
-      <c r="A236" s="31"/>
+      <c r="A236" s="34"/>
     </row>
     <row r="237">
-      <c r="A237" s="31"/>
+      <c r="A237" s="34"/>
     </row>
     <row r="238">
-      <c r="A238" s="31"/>
+      <c r="A238" s="34"/>
     </row>
     <row r="239">
-      <c r="A239" s="31"/>
+      <c r="A239" s="34"/>
     </row>
     <row r="240">
-      <c r="A240" s="31"/>
+      <c r="A240" s="34"/>
     </row>
     <row r="241">
-      <c r="A241" s="31"/>
+      <c r="A241" s="34"/>
     </row>
     <row r="242">
-      <c r="A242" s="31"/>
+      <c r="A242" s="34"/>
     </row>
     <row r="243">
-      <c r="A243" s="31"/>
+      <c r="A243" s="34"/>
     </row>
     <row r="244">
-      <c r="A244" s="31"/>
+      <c r="A244" s="34"/>
     </row>
     <row r="245">
-      <c r="A245" s="31"/>
+      <c r="A245" s="34"/>
     </row>
     <row r="246">
-      <c r="A246" s="31"/>
+      <c r="A246" s="34"/>
     </row>
     <row r="247">
-      <c r="A247" s="31"/>
+      <c r="A247" s="34"/>
     </row>
     <row r="248">
-      <c r="A248" s="31"/>
+      <c r="A248" s="34"/>
     </row>
     <row r="249">
-      <c r="A249" s="31"/>
+      <c r="A249" s="34"/>
     </row>
     <row r="250">
-      <c r="A250" s="31"/>
+      <c r="A250" s="34"/>
     </row>
     <row r="251">
-      <c r="A251" s="31"/>
+      <c r="A251" s="34"/>
     </row>
     <row r="252">
-      <c r="A252" s="31"/>
+      <c r="A252" s="34"/>
     </row>
     <row r="253">
-      <c r="A253" s="31"/>
+      <c r="A253" s="34"/>
     </row>
     <row r="254">
-      <c r="A254" s="31"/>
+      <c r="A254" s="34"/>
     </row>
     <row r="255">
-      <c r="A255" s="31"/>
+      <c r="A255" s="34"/>
     </row>
     <row r="256">
-      <c r="A256" s="31"/>
+      <c r="A256" s="34"/>
     </row>
     <row r="257">
-      <c r="A257" s="31"/>
+      <c r="A257" s="34"/>
     </row>
     <row r="258">
-      <c r="A258" s="31"/>
+      <c r="A258" s="34"/>
     </row>
     <row r="259">
-      <c r="A259" s="31"/>
+      <c r="A259" s="34"/>
     </row>
     <row r="260">
-      <c r="A260" s="31"/>
+      <c r="A260" s="34"/>
     </row>
     <row r="261">
-      <c r="A261" s="31"/>
+      <c r="A261" s="34"/>
     </row>
     <row r="262">
-      <c r="A262" s="31"/>
+      <c r="A262" s="34"/>
     </row>
     <row r="263">
-      <c r="A263" s="31"/>
+      <c r="A263" s="34"/>
     </row>
     <row r="264">
-      <c r="A264" s="31"/>
+      <c r="A264" s="34"/>
     </row>
     <row r="265">
-      <c r="A265" s="31"/>
+      <c r="A265" s="34"/>
     </row>
     <row r="266">
-      <c r="A266" s="31"/>
+      <c r="A266" s="34"/>
     </row>
     <row r="267">
-      <c r="A267" s="31"/>
+      <c r="A267" s="34"/>
     </row>
     <row r="268">
-      <c r="A268" s="31"/>
+      <c r="A268" s="34"/>
     </row>
     <row r="269">
-      <c r="A269" s="31"/>
+      <c r="A269" s="34"/>
     </row>
     <row r="270">
-      <c r="A270" s="31"/>
+      <c r="A270" s="34"/>
     </row>
     <row r="271">
-      <c r="A271" s="31"/>
+      <c r="A271" s="34"/>
     </row>
     <row r="272">
-      <c r="A272" s="31"/>
+      <c r="A272" s="34"/>
     </row>
     <row r="273">
-      <c r="A273" s="31"/>
+      <c r="A273" s="34"/>
     </row>
     <row r="274">
-      <c r="A274" s="31"/>
+      <c r="A274" s="34"/>
     </row>
     <row r="275">
-      <c r="A275" s="31"/>
+      <c r="A275" s="34"/>
     </row>
     <row r="276">
-      <c r="A276" s="31"/>
+      <c r="A276" s="34"/>
     </row>
     <row r="277">
-      <c r="A277" s="31"/>
+      <c r="A277" s="34"/>
     </row>
     <row r="278">
-      <c r="A278" s="31"/>
+      <c r="A278" s="34"/>
     </row>
     <row r="279">
-      <c r="A279" s="31"/>
+      <c r="A279" s="34"/>
     </row>
     <row r="280">
-      <c r="A280" s="31"/>
+      <c r="A280" s="34"/>
     </row>
     <row r="281">
-      <c r="A281" s="31"/>
+      <c r="A281" s="34"/>
     </row>
     <row r="282">
-      <c r="A282" s="31"/>
+      <c r="A282" s="34"/>
     </row>
     <row r="283">
-      <c r="A283" s="31"/>
+      <c r="A283" s="34"/>
     </row>
     <row r="284">
-      <c r="A284" s="31"/>
+      <c r="A284" s="34"/>
     </row>
     <row r="285">
-      <c r="A285" s="31"/>
+      <c r="A285" s="34"/>
     </row>
     <row r="286">
-      <c r="A286" s="31"/>
+      <c r="A286" s="34"/>
     </row>
     <row r="287">
-      <c r="A287" s="31"/>
+      <c r="A287" s="34"/>
     </row>
     <row r="288">
-      <c r="A288" s="31"/>
+      <c r="A288" s="34"/>
     </row>
     <row r="289">
-      <c r="A289" s="31"/>
+      <c r="A289" s="34"/>
     </row>
     <row r="290">
-      <c r="A290" s="31"/>
+      <c r="A290" s="34"/>
     </row>
     <row r="291">
-      <c r="A291" s="31"/>
+      <c r="A291" s="34"/>
     </row>
     <row r="292">
-      <c r="A292" s="31"/>
+      <c r="A292" s="34"/>
     </row>
     <row r="293">
-      <c r="A293" s="31"/>
+      <c r="A293" s="34"/>
     </row>
     <row r="294">
-      <c r="A294" s="31"/>
+      <c r="A294" s="34"/>
     </row>
     <row r="295">
-      <c r="A295" s="31"/>
+      <c r="A295" s="34"/>
     </row>
     <row r="296">
-      <c r="A296" s="31"/>
+      <c r="A296" s="34"/>
     </row>
     <row r="297">
-      <c r="A297" s="31"/>
+      <c r="A297" s="34"/>
     </row>
     <row r="298">
-      <c r="A298" s="31"/>
+      <c r="A298" s="34"/>
     </row>
     <row r="299">
-      <c r="A299" s="31"/>
+      <c r="A299" s="34"/>
     </row>
     <row r="300">
-      <c r="A300" s="31"/>
+      <c r="A300" s="34"/>
     </row>
     <row r="301">
-      <c r="A301" s="31"/>
+      <c r="A301" s="34"/>
     </row>
     <row r="302">
-      <c r="A302" s="31"/>
+      <c r="A302" s="34"/>
     </row>
     <row r="303">
-      <c r="A303" s="31"/>
+      <c r="A303" s="34"/>
     </row>
     <row r="304">
-      <c r="A304" s="31"/>
+      <c r="A304" s="34"/>
     </row>
     <row r="305">
-      <c r="A305" s="31"/>
+      <c r="A305" s="34"/>
     </row>
     <row r="306">
-      <c r="A306" s="31"/>
+      <c r="A306" s="34"/>
     </row>
     <row r="307">
-      <c r="A307" s="31"/>
+      <c r="A307" s="34"/>
     </row>
     <row r="308">
-      <c r="A308" s="31"/>
+      <c r="A308" s="34"/>
     </row>
     <row r="309">
-      <c r="A309" s="31"/>
+      <c r="A309" s="34"/>
     </row>
     <row r="310">
-      <c r="A310" s="31"/>
+      <c r="A310" s="34"/>
     </row>
     <row r="311">
-      <c r="A311" s="31"/>
+      <c r="A311" s="34"/>
     </row>
     <row r="312">
-      <c r="A312" s="31"/>
+      <c r="A312" s="34"/>
     </row>
     <row r="313">
-      <c r="A313" s="31"/>
+      <c r="A313" s="34"/>
     </row>
     <row r="314">
-      <c r="A314" s="31"/>
+      <c r="A314" s="34"/>
     </row>
     <row r="315">
-      <c r="A315" s="31"/>
+      <c r="A315" s="34"/>
     </row>
     <row r="316">
-      <c r="A316" s="31"/>
+      <c r="A316" s="34"/>
     </row>
     <row r="317">
-      <c r="A317" s="31"/>
+      <c r="A317" s="34"/>
     </row>
     <row r="318">
-      <c r="A318" s="31"/>
+      <c r="A318" s="34"/>
     </row>
     <row r="319">
-      <c r="A319" s="31"/>
+      <c r="A319" s="34"/>
     </row>
     <row r="320">
-      <c r="A320" s="31"/>
+      <c r="A320" s="34"/>
     </row>
     <row r="321">
-      <c r="A321" s="31"/>
+      <c r="A321" s="34"/>
     </row>
     <row r="322">
-      <c r="A322" s="31"/>
+      <c r="A322" s="34"/>
     </row>
     <row r="323">
-      <c r="A323" s="31"/>
+      <c r="A323" s="34"/>
     </row>
     <row r="324">
-      <c r="A324" s="31"/>
+      <c r="A324" s="34"/>
     </row>
     <row r="325">
-      <c r="A325" s="31"/>
+      <c r="A325" s="34"/>
     </row>
     <row r="326">
-      <c r="A326" s="31"/>
+      <c r="A326" s="34"/>
     </row>
     <row r="327">
-      <c r="A327" s="31"/>
+      <c r="A327" s="34"/>
     </row>
     <row r="328">
-      <c r="A328" s="31"/>
+      <c r="A328" s="34"/>
     </row>
     <row r="329">
-      <c r="A329" s="31"/>
+      <c r="A329" s="34"/>
     </row>
     <row r="330">
-      <c r="A330" s="31"/>
+      <c r="A330" s="34"/>
     </row>
     <row r="331">
-      <c r="A331" s="31"/>
+      <c r="A331" s="34"/>
     </row>
     <row r="332">
-      <c r="A332" s="31"/>
+      <c r="A332" s="34"/>
     </row>
     <row r="333">
-      <c r="A333" s="31"/>
+      <c r="A333" s="34"/>
     </row>
     <row r="334">
-      <c r="A334" s="31"/>
+      <c r="A334" s="34"/>
     </row>
     <row r="335">
-      <c r="A335" s="31"/>
+      <c r="A335" s="34"/>
     </row>
     <row r="336">
-      <c r="A336" s="31"/>
+      <c r="A336" s="34"/>
     </row>
     <row r="337">
-      <c r="A337" s="31"/>
+      <c r="A337" s="34"/>
     </row>
     <row r="338">
-      <c r="A338" s="31"/>
+      <c r="A338" s="34"/>
     </row>
     <row r="339">
-      <c r="A339" s="31"/>
+      <c r="A339" s="34"/>
     </row>
     <row r="340">
-      <c r="A340" s="31"/>
+      <c r="A340" s="34"/>
     </row>
     <row r="341">
-      <c r="A341" s="31"/>
+      <c r="A341" s="34"/>
     </row>
     <row r="342">
-      <c r="A342" s="31"/>
+      <c r="A342" s="34"/>
     </row>
     <row r="343">
-      <c r="A343" s="31"/>
+      <c r="A343" s="34"/>
     </row>
     <row r="344">
-      <c r="A344" s="31"/>
+      <c r="A344" s="34"/>
     </row>
     <row r="345">
-      <c r="A345" s="31"/>
+      <c r="A345" s="34"/>
     </row>
     <row r="346">
-      <c r="A346" s="31"/>
+      <c r="A346" s="34"/>
     </row>
     <row r="347">
-      <c r="A347" s="31"/>
+      <c r="A347" s="34"/>
     </row>
     <row r="348">
-      <c r="A348" s="31"/>
+      <c r="A348" s="34"/>
     </row>
     <row r="349">
-      <c r="A349" s="31"/>
+      <c r="A349" s="34"/>
     </row>
     <row r="350">
-      <c r="A350" s="31"/>
+      <c r="A350" s="34"/>
     </row>
     <row r="351">
-      <c r="A351" s="31"/>
+      <c r="A351" s="34"/>
     </row>
     <row r="352">
-      <c r="A352" s="31"/>
+      <c r="A352" s="34"/>
     </row>
     <row r="353">
-      <c r="A353" s="31"/>
+      <c r="A353" s="34"/>
     </row>
     <row r="354">
-      <c r="A354" s="31"/>
+      <c r="A354" s="34"/>
     </row>
     <row r="355">
-      <c r="A355" s="31"/>
+      <c r="A355" s="34"/>
     </row>
     <row r="356">
-      <c r="A356" s="31"/>
+      <c r="A356" s="34"/>
     </row>
     <row r="357">
-      <c r="A357" s="31"/>
+      <c r="A357" s="34"/>
     </row>
     <row r="358">
-      <c r="A358" s="31"/>
+      <c r="A358" s="34"/>
     </row>
     <row r="359">
-      <c r="A359" s="31"/>
+      <c r="A359" s="34"/>
     </row>
     <row r="360">
-      <c r="A360" s="31"/>
+      <c r="A360" s="34"/>
     </row>
     <row r="361">
-      <c r="A361" s="31"/>
+      <c r="A361" s="34"/>
     </row>
     <row r="362">
-      <c r="A362" s="31"/>
+      <c r="A362" s="34"/>
     </row>
     <row r="363">
-      <c r="A363" s="31"/>
+      <c r="A363" s="34"/>
     </row>
     <row r="364">
-      <c r="A364" s="31"/>
+      <c r="A364" s="34"/>
     </row>
     <row r="365">
-      <c r="A365" s="31"/>
+      <c r="A365" s="34"/>
     </row>
     <row r="366">
-      <c r="A366" s="31"/>
+      <c r="A366" s="34"/>
     </row>
     <row r="367">
-      <c r="A367" s="31"/>
+      <c r="A367" s="34"/>
     </row>
     <row r="368">
-      <c r="A368" s="31"/>
+      <c r="A368" s="34"/>
     </row>
     <row r="369">
-      <c r="A369" s="31"/>
+      <c r="A369" s="34"/>
     </row>
     <row r="370">
-      <c r="A370" s="31"/>
+      <c r="A370" s="34"/>
     </row>
     <row r="371">
-      <c r="A371" s="31"/>
+      <c r="A371" s="34"/>
     </row>
     <row r="372">
-      <c r="A372" s="31"/>
+      <c r="A372" s="34"/>
     </row>
     <row r="373">
-      <c r="A373" s="31"/>
+      <c r="A373" s="34"/>
     </row>
     <row r="374">
-      <c r="A374" s="31"/>
+      <c r="A374" s="34"/>
     </row>
     <row r="375">
-      <c r="A375" s="31"/>
+      <c r="A375" s="34"/>
     </row>
     <row r="376">
-      <c r="A376" s="31"/>
+      <c r="A376" s="34"/>
     </row>
     <row r="377">
-      <c r="A377" s="31"/>
+      <c r="A377" s="34"/>
     </row>
     <row r="378">
-      <c r="A378" s="31"/>
+      <c r="A378" s="34"/>
     </row>
     <row r="379">
-      <c r="A379" s="31"/>
+      <c r="A379" s="34"/>
     </row>
     <row r="380">
-      <c r="A380" s="31"/>
+      <c r="A380" s="34"/>
     </row>
     <row r="381">
-      <c r="A381" s="31"/>
+      <c r="A381" s="34"/>
     </row>
     <row r="382">
-      <c r="A382" s="31"/>
+      <c r="A382" s="34"/>
     </row>
     <row r="383">
-      <c r="A383" s="31"/>
+      <c r="A383" s="34"/>
     </row>
     <row r="384">
-      <c r="A384" s="31"/>
+      <c r="A384" s="34"/>
     </row>
     <row r="385">
-      <c r="A385" s="31"/>
+      <c r="A385" s="34"/>
     </row>
     <row r="386">
-      <c r="A386" s="31"/>
+      <c r="A386" s="34"/>
     </row>
     <row r="387">
-      <c r="A387" s="31"/>
+      <c r="A387" s="34"/>
     </row>
     <row r="388">
-      <c r="A388" s="31"/>
+      <c r="A388" s="34"/>
     </row>
     <row r="389">
-      <c r="A389" s="31"/>
+      <c r="A389" s="34"/>
     </row>
     <row r="390">
-      <c r="A390" s="31"/>
+      <c r="A390" s="34"/>
     </row>
     <row r="391">
-      <c r="A391" s="31"/>
+      <c r="A391" s="34"/>
     </row>
     <row r="392">
-      <c r="A392" s="31"/>
+      <c r="A392" s="34"/>
     </row>
     <row r="393">
-      <c r="A393" s="31"/>
+      <c r="A393" s="34"/>
     </row>
     <row r="394">
-      <c r="A394" s="31"/>
+      <c r="A394" s="34"/>
     </row>
     <row r="395">
-      <c r="A395" s="31"/>
+      <c r="A395" s="34"/>
     </row>
     <row r="396">
-      <c r="A396" s="31"/>
+      <c r="A396" s="34"/>
     </row>
     <row r="397">
-      <c r="A397" s="31"/>
+      <c r="A397" s="34"/>
     </row>
     <row r="398">
-      <c r="A398" s="31"/>
+      <c r="A398" s="34"/>
     </row>
     <row r="399">
-      <c r="A399" s="31"/>
+      <c r="A399" s="34"/>
     </row>
     <row r="400">
-      <c r="A400" s="31"/>
+      <c r="A400" s="34"/>
     </row>
     <row r="401">
-      <c r="A401" s="31"/>
+      <c r="A401" s="34"/>
     </row>
     <row r="402">
-      <c r="A402" s="31"/>
+      <c r="A402" s="34"/>
     </row>
     <row r="403">
-      <c r="A403" s="31"/>
+      <c r="A403" s="34"/>
     </row>
     <row r="404">
-      <c r="A404" s="31"/>
+      <c r="A404" s="34"/>
     </row>
     <row r="405">
-      <c r="A405" s="31"/>
+      <c r="A405" s="34"/>
     </row>
     <row r="406">
-      <c r="A406" s="31"/>
+      <c r="A406" s="34"/>
     </row>
     <row r="407">
-      <c r="A407" s="31"/>
+      <c r="A407" s="34"/>
     </row>
     <row r="408">
-      <c r="A408" s="31"/>
+      <c r="A408" s="34"/>
     </row>
     <row r="409">
-      <c r="A409" s="31"/>
+      <c r="A409" s="34"/>
     </row>
     <row r="410">
-      <c r="A410" s="31"/>
+      <c r="A410" s="34"/>
     </row>
     <row r="411">
-      <c r="A411" s="31"/>
+      <c r="A411" s="34"/>
     </row>
     <row r="412">
-      <c r="A412" s="31"/>
+      <c r="A412" s="34"/>
     </row>
     <row r="413">
-      <c r="A413" s="31"/>
+      <c r="A413" s="34"/>
     </row>
     <row r="414">
-      <c r="A414" s="31"/>
+      <c r="A414" s="34"/>
     </row>
     <row r="415">
-      <c r="A415" s="31"/>
+      <c r="A415" s="34"/>
     </row>
     <row r="416">
-      <c r="A416" s="31"/>
+      <c r="A416" s="34"/>
     </row>
     <row r="417">
-      <c r="A417" s="31"/>
+      <c r="A417" s="34"/>
     </row>
     <row r="418">
-      <c r="A418" s="31"/>
+      <c r="A418" s="34"/>
     </row>
     <row r="419">
-      <c r="A419" s="31"/>
+      <c r="A419" s="34"/>
     </row>
     <row r="420">
-      <c r="A420" s="31"/>
+      <c r="A420" s="34"/>
     </row>
     <row r="421">
-      <c r="A421" s="31"/>
+      <c r="A421" s="34"/>
     </row>
     <row r="422">
-      <c r="A422" s="31"/>
+      <c r="A422" s="34"/>
     </row>
     <row r="423">
-      <c r="A423" s="31"/>
+      <c r="A423" s="34"/>
     </row>
     <row r="424">
-      <c r="A424" s="31"/>
+      <c r="A424" s="34"/>
     </row>
     <row r="425">
-      <c r="A425" s="31"/>
+      <c r="A425" s="34"/>
     </row>
     <row r="426">
-      <c r="A426" s="31"/>
+      <c r="A426" s="34"/>
     </row>
     <row r="427">
-      <c r="A427" s="31"/>
+      <c r="A427" s="34"/>
     </row>
     <row r="428">
-      <c r="A428" s="31"/>
+      <c r="A428" s="34"/>
     </row>
     <row r="429">
-      <c r="A429" s="31"/>
+      <c r="A429" s="34"/>
     </row>
     <row r="430">
-      <c r="A430" s="31"/>
+      <c r="A430" s="34"/>
     </row>
     <row r="431">
-      <c r="A431" s="31"/>
+      <c r="A431" s="34"/>
     </row>
     <row r="432">
-      <c r="A432" s="31"/>
+      <c r="A432" s="34"/>
     </row>
     <row r="433">
-      <c r="A433" s="31"/>
+      <c r="A433" s="34"/>
     </row>
     <row r="434">
-      <c r="A434" s="31"/>
+      <c r="A434" s="34"/>
     </row>
     <row r="435">
-      <c r="A435" s="31"/>
+      <c r="A435" s="34"/>
     </row>
     <row r="436">
-      <c r="A436" s="31"/>
+      <c r="A436" s="34"/>
     </row>
     <row r="437">
-      <c r="A437" s="31"/>
+      <c r="A437" s="34"/>
     </row>
     <row r="438">
-      <c r="A438" s="31"/>
+      <c r="A438" s="34"/>
     </row>
     <row r="439">
-      <c r="A439" s="31"/>
+      <c r="A439" s="34"/>
     </row>
     <row r="440">
-      <c r="A440" s="31"/>
+      <c r="A440" s="34"/>
     </row>
     <row r="441">
-      <c r="A441" s="31"/>
+      <c r="A441" s="34"/>
     </row>
     <row r="442">
-      <c r="A442" s="31"/>
+      <c r="A442" s="34"/>
     </row>
     <row r="443">
-      <c r="A443" s="31"/>
+      <c r="A443" s="34"/>
     </row>
     <row r="444">
-      <c r="A444" s="31"/>
+      <c r="A444" s="34"/>
     </row>
     <row r="445">
-      <c r="A445" s="31"/>
+      <c r="A445" s="34"/>
     </row>
     <row r="446">
-      <c r="A446" s="31"/>
+      <c r="A446" s="34"/>
     </row>
     <row r="447">
-      <c r="A447" s="31"/>
+      <c r="A447" s="34"/>
     </row>
     <row r="448">
-      <c r="A448" s="31"/>
+      <c r="A448" s="34"/>
     </row>
     <row r="449">
-      <c r="A449" s="31"/>
+      <c r="A449" s="34"/>
     </row>
     <row r="450">
-      <c r="A450" s="31"/>
+      <c r="A450" s="34"/>
     </row>
     <row r="451">
-      <c r="A451" s="31"/>
+      <c r="A451" s="34"/>
     </row>
     <row r="452">
-      <c r="A452" s="31"/>
+      <c r="A452" s="34"/>
     </row>
     <row r="453">
-      <c r="A453" s="31"/>
+      <c r="A453" s="34"/>
     </row>
     <row r="454">
-      <c r="A454" s="31"/>
+      <c r="A454" s="34"/>
     </row>
     <row r="455">
-      <c r="A455" s="31"/>
+      <c r="A455" s="34"/>
     </row>
     <row r="456">
-      <c r="A456" s="31"/>
+      <c r="A456" s="34"/>
     </row>
     <row r="457">
-      <c r="A457" s="31"/>
+      <c r="A457" s="34"/>
     </row>
     <row r="458">
-      <c r="A458" s="31"/>
+      <c r="A458" s="34"/>
     </row>
     <row r="459">
-      <c r="A459" s="31"/>
+      <c r="A459" s="34"/>
     </row>
     <row r="460">
-      <c r="A460" s="31"/>
+      <c r="A460" s="34"/>
     </row>
     <row r="461">
-      <c r="A461" s="31"/>
+      <c r="A461" s="34"/>
     </row>
     <row r="462">
-      <c r="A462" s="31"/>
+      <c r="A462" s="34"/>
     </row>
     <row r="463">
-      <c r="A463" s="31"/>
+      <c r="A463" s="34"/>
     </row>
     <row r="464">
-      <c r="A464" s="31"/>
+      <c r="A464" s="34"/>
     </row>
     <row r="465">
-      <c r="A465" s="31"/>
+      <c r="A465" s="34"/>
     </row>
     <row r="466">
-      <c r="A466" s="31"/>
+      <c r="A466" s="34"/>
     </row>
     <row r="467">
-      <c r="A467" s="31"/>
+      <c r="A467" s="34"/>
     </row>
     <row r="468">
-      <c r="A468" s="31"/>
+      <c r="A468" s="34"/>
     </row>
     <row r="469">
-      <c r="A469" s="31"/>
+      <c r="A469" s="34"/>
     </row>
     <row r="470">
-      <c r="A470" s="31"/>
+      <c r="A470" s="34"/>
     </row>
     <row r="471">
-      <c r="A471" s="31"/>
+      <c r="A471" s="34"/>
     </row>
     <row r="472">
-      <c r="A472" s="31"/>
+      <c r="A472" s="34"/>
     </row>
     <row r="473">
-      <c r="A473" s="31"/>
+      <c r="A473" s="34"/>
     </row>
     <row r="474">
-      <c r="A474" s="31"/>
+      <c r="A474" s="34"/>
     </row>
     <row r="475">
-      <c r="A475" s="31"/>
+      <c r="A475" s="34"/>
     </row>
     <row r="476">
-      <c r="A476" s="31"/>
+      <c r="A476" s="34"/>
     </row>
     <row r="477">
-      <c r="A477" s="31"/>
+      <c r="A477" s="34"/>
     </row>
     <row r="478">
-      <c r="A478" s="31"/>
+      <c r="A478" s="34"/>
     </row>
     <row r="479">
-      <c r="A479" s="31"/>
+      <c r="A479" s="34"/>
     </row>
     <row r="480">
-      <c r="A480" s="31"/>
+      <c r="A480" s="34"/>
     </row>
     <row r="481">
-      <c r="A481" s="31"/>
+      <c r="A481" s="34"/>
     </row>
     <row r="482">
-      <c r="A482" s="31"/>
+      <c r="A482" s="34"/>
     </row>
     <row r="483">
-      <c r="A483" s="31"/>
+      <c r="A483" s="34"/>
     </row>
     <row r="484">
-      <c r="A484" s="31"/>
+      <c r="A484" s="34"/>
     </row>
     <row r="485">
-      <c r="A485" s="31"/>
+      <c r="A485" s="34"/>
     </row>
     <row r="486">
-      <c r="A486" s="31"/>
+      <c r="A486" s="34"/>
     </row>
     <row r="487">
-      <c r="A487" s="31"/>
+      <c r="A487" s="34"/>
     </row>
     <row r="488">
-      <c r="A488" s="31"/>
+      <c r="A488" s="34"/>
     </row>
     <row r="489">
-      <c r="A489" s="31"/>
+      <c r="A489" s="34"/>
     </row>
     <row r="490">
-      <c r="A490" s="31"/>
+      <c r="A490" s="34"/>
     </row>
     <row r="491">
-      <c r="A491" s="31"/>
+      <c r="A491" s="34"/>
     </row>
     <row r="492">
-      <c r="A492" s="31"/>
+      <c r="A492" s="34"/>
     </row>
     <row r="493">
-      <c r="A493" s="31"/>
+      <c r="A493" s="34"/>
     </row>
     <row r="494">
-      <c r="A494" s="31"/>
+      <c r="A494" s="34"/>
     </row>
     <row r="495">
-      <c r="A495" s="31"/>
+      <c r="A495" s="34"/>
     </row>
     <row r="496">
-      <c r="A496" s="31"/>
+      <c r="A496" s="34"/>
     </row>
     <row r="497">
-      <c r="A497" s="31"/>
+      <c r="A497" s="34"/>
     </row>
     <row r="498">
-      <c r="A498" s="31"/>
+      <c r="A498" s="34"/>
     </row>
     <row r="499">
-      <c r="A499" s="31"/>
+      <c r="A499" s="34"/>
     </row>
     <row r="500">
-      <c r="A500" s="31"/>
+      <c r="A500" s="34"/>
     </row>
     <row r="501">
-      <c r="A501" s="31"/>
+      <c r="A501" s="34"/>
     </row>
     <row r="502">
-      <c r="A502" s="31"/>
+      <c r="A502" s="34"/>
     </row>
     <row r="503">
-      <c r="A503" s="31"/>
+      <c r="A503" s="34"/>
     </row>
     <row r="504">
-      <c r="A504" s="31"/>
+      <c r="A504" s="34"/>
     </row>
     <row r="505">
-      <c r="A505" s="31"/>
+      <c r="A505" s="34"/>
     </row>
     <row r="506">
-      <c r="A506" s="31"/>
+      <c r="A506" s="34"/>
     </row>
     <row r="507">
-      <c r="A507" s="31"/>
+      <c r="A507" s="34"/>
     </row>
     <row r="508">
-      <c r="A508" s="31"/>
+      <c r="A508" s="34"/>
     </row>
     <row r="509">
-      <c r="A509" s="31"/>
+      <c r="A509" s="34"/>
     </row>
     <row r="510">
-      <c r="A510" s="31"/>
+      <c r="A510" s="34"/>
     </row>
     <row r="511">
-      <c r="A511" s="31"/>
+      <c r="A511" s="34"/>
     </row>
     <row r="512">
-      <c r="A512" s="31"/>
+      <c r="A512" s="34"/>
     </row>
     <row r="513">
-      <c r="A513" s="31"/>
+      <c r="A513" s="34"/>
     </row>
     <row r="514">
-      <c r="A514" s="31"/>
+      <c r="A514" s="34"/>
     </row>
     <row r="515">
-      <c r="A515" s="31"/>
+      <c r="A515" s="34"/>
     </row>
     <row r="516">
-      <c r="A516" s="31"/>
+      <c r="A516" s="34"/>
     </row>
     <row r="517">
-      <c r="A517" s="31"/>
+      <c r="A517" s="34"/>
     </row>
     <row r="518">
-      <c r="A518" s="31"/>
+      <c r="A518" s="34"/>
     </row>
     <row r="519">
-      <c r="A519" s="31"/>
+      <c r="A519" s="34"/>
     </row>
     <row r="520">
-      <c r="A520" s="31"/>
+      <c r="A520" s="34"/>
     </row>
     <row r="521">
-      <c r="A521" s="31"/>
+      <c r="A521" s="34"/>
     </row>
     <row r="522">
-      <c r="A522" s="31"/>
+      <c r="A522" s="34"/>
     </row>
     <row r="523">
-      <c r="A523" s="31"/>
+      <c r="A523" s="34"/>
     </row>
     <row r="524">
-      <c r="A524" s="31"/>
+      <c r="A524" s="34"/>
     </row>
     <row r="525">
-      <c r="A525" s="31"/>
+      <c r="A525" s="34"/>
     </row>
     <row r="526">
-      <c r="A526" s="31"/>
+      <c r="A526" s="34"/>
     </row>
     <row r="527">
-      <c r="A527" s="31"/>
+      <c r="A527" s="34"/>
     </row>
     <row r="528">
-      <c r="A528" s="31"/>
+      <c r="A528" s="34"/>
     </row>
     <row r="529">
-      <c r="A529" s="31"/>
+      <c r="A529" s="34"/>
     </row>
     <row r="530">
-      <c r="A530" s="31"/>
+      <c r="A530" s="34"/>
     </row>
     <row r="531">
-      <c r="A531" s="31"/>
+      <c r="A531" s="34"/>
     </row>
     <row r="532">
-      <c r="A532" s="31"/>
+      <c r="A532" s="34"/>
     </row>
     <row r="533">
-      <c r="A533" s="31"/>
+      <c r="A533" s="34"/>
     </row>
     <row r="534">
-      <c r="A534" s="31"/>
+      <c r="A534" s="34"/>
     </row>
     <row r="535">
-      <c r="A535" s="31"/>
+      <c r="A535" s="34"/>
     </row>
     <row r="536">
-      <c r="A536" s="31"/>
+      <c r="A536" s="34"/>
     </row>
     <row r="537">
-      <c r="A537" s="31"/>
+      <c r="A537" s="34"/>
     </row>
     <row r="538">
-      <c r="A538" s="31"/>
+      <c r="A538" s="34"/>
     </row>
     <row r="539">
-      <c r="A539" s="31"/>
+      <c r="A539" s="34"/>
     </row>
     <row r="540">
-      <c r="A540" s="31"/>
+      <c r="A540" s="34"/>
     </row>
     <row r="541">
-      <c r="A541" s="31"/>
+      <c r="A541" s="34"/>
     </row>
     <row r="542">
-      <c r="A542" s="31"/>
+      <c r="A542" s="34"/>
     </row>
     <row r="543">
-      <c r="A543" s="31"/>
+      <c r="A543" s="34"/>
     </row>
     <row r="544">
-      <c r="A544" s="31"/>
+      <c r="A544" s="34"/>
     </row>
     <row r="545">
-      <c r="A545" s="31"/>
+      <c r="A545" s="34"/>
     </row>
     <row r="546">
-      <c r="A546" s="31"/>
+      <c r="A546" s="34"/>
     </row>
     <row r="547">
-      <c r="A547" s="31"/>
+      <c r="A547" s="34"/>
     </row>
     <row r="548">
-      <c r="A548" s="31"/>
+      <c r="A548" s="34"/>
     </row>
     <row r="549">
-      <c r="A549" s="31"/>
+      <c r="A549" s="34"/>
     </row>
     <row r="550">
-      <c r="A550" s="31"/>
+      <c r="A550" s="34"/>
     </row>
     <row r="551">
-      <c r="A551" s="31"/>
+      <c r="A551" s="34"/>
     </row>
     <row r="552">
-      <c r="A552" s="31"/>
+      <c r="A552" s="34"/>
     </row>
     <row r="553">
-      <c r="A553" s="31"/>
+      <c r="A553" s="34"/>
     </row>
     <row r="554">
-      <c r="A554" s="31"/>
+      <c r="A554" s="34"/>
     </row>
     <row r="555">
-      <c r="A555" s="31"/>
+      <c r="A555" s="34"/>
     </row>
     <row r="556">
-      <c r="A556" s="31"/>
+      <c r="A556" s="34"/>
     </row>
     <row r="557">
-      <c r="A557" s="31"/>
+      <c r="A557" s="34"/>
     </row>
     <row r="558">
-      <c r="A558" s="31"/>
+      <c r="A558" s="34"/>
     </row>
     <row r="559">
-      <c r="A559" s="31"/>
+      <c r="A559" s="34"/>
     </row>
     <row r="560">
-      <c r="A560" s="31"/>
+      <c r="A560" s="34"/>
     </row>
     <row r="561">
-      <c r="A561" s="31"/>
+      <c r="A561" s="34"/>
     </row>
     <row r="562">
-      <c r="A562" s="31"/>
+      <c r="A562" s="34"/>
     </row>
     <row r="563">
-      <c r="A563" s="31"/>
+      <c r="A563" s="34"/>
     </row>
     <row r="564">
-      <c r="A564" s="31"/>
+      <c r="A564" s="34"/>
     </row>
     <row r="565">
-      <c r="A565" s="31"/>
+      <c r="A565" s="34"/>
     </row>
     <row r="566">
-      <c r="A566" s="31"/>
+      <c r="A566" s="34"/>
     </row>
     <row r="567">
-      <c r="A567" s="31"/>
+      <c r="A567" s="34"/>
     </row>
     <row r="568">
-      <c r="A568" s="31"/>
+      <c r="A568" s="34"/>
     </row>
     <row r="569">
-      <c r="A569" s="31"/>
+      <c r="A569" s="34"/>
     </row>
     <row r="570">
-      <c r="A570" s="31"/>
+      <c r="A570" s="34"/>
     </row>
     <row r="571">
-      <c r="A571" s="31"/>
+      <c r="A571" s="34"/>
     </row>
     <row r="572">
-      <c r="A572" s="31"/>
+      <c r="A572" s="34"/>
     </row>
     <row r="573">
-      <c r="A573" s="31"/>
+      <c r="A573" s="34"/>
     </row>
     <row r="574">
-      <c r="A574" s="31"/>
+      <c r="A574" s="34"/>
     </row>
     <row r="575">
-      <c r="A575" s="31"/>
+      <c r="A575" s="34"/>
     </row>
     <row r="576">
-      <c r="A576" s="31"/>
+      <c r="A576" s="34"/>
     </row>
     <row r="577">
-      <c r="A577" s="31"/>
+      <c r="A577" s="34"/>
     </row>
     <row r="578">
-      <c r="A578" s="31"/>
+      <c r="A578" s="34"/>
     </row>
     <row r="579">
-      <c r="A579" s="31"/>
+      <c r="A579" s="34"/>
     </row>
     <row r="580">
-      <c r="A580" s="31"/>
+      <c r="A580" s="34"/>
     </row>
     <row r="581">
-      <c r="A581" s="31"/>
+      <c r="A581" s="34"/>
     </row>
     <row r="582">
-      <c r="A582" s="31"/>
+      <c r="A582" s="34"/>
     </row>
     <row r="583">
-      <c r="A583" s="31"/>
+      <c r="A583" s="34"/>
     </row>
     <row r="584">
-      <c r="A584" s="31"/>
+      <c r="A584" s="34"/>
     </row>
     <row r="585">
-      <c r="A585" s="31"/>
+      <c r="A585" s="34"/>
     </row>
     <row r="586">
-      <c r="A586" s="31"/>
+      <c r="A586" s="34"/>
     </row>
     <row r="587">
-      <c r="A587" s="31"/>
+      <c r="A587" s="34"/>
     </row>
     <row r="588">
-      <c r="A588" s="31"/>
+      <c r="A588" s="34"/>
     </row>
     <row r="589">
-      <c r="A589" s="31"/>
+      <c r="A589" s="34"/>
     </row>
     <row r="590">
-      <c r="A590" s="31"/>
+      <c r="A590" s="34"/>
     </row>
     <row r="591">
-      <c r="A591" s="31"/>
+      <c r="A591" s="34"/>
     </row>
     <row r="592">
-      <c r="A592" s="31"/>
+      <c r="A592" s="34"/>
     </row>
     <row r="593">
-      <c r="A593" s="31"/>
+      <c r="A593" s="34"/>
     </row>
     <row r="594">
-      <c r="A594" s="31"/>
+      <c r="A594" s="34"/>
     </row>
     <row r="595">
-      <c r="A595" s="31"/>
+      <c r="A595" s="34"/>
     </row>
     <row r="596">
-      <c r="A596" s="31"/>
+      <c r="A596" s="34"/>
     </row>
     <row r="597">
-      <c r="A597" s="31"/>
+      <c r="A597" s="34"/>
     </row>
     <row r="598">
-      <c r="A598" s="31"/>
+      <c r="A598" s="34"/>
     </row>
     <row r="599">
-      <c r="A599" s="31"/>
+      <c r="A599" s="34"/>
     </row>
     <row r="600">
-      <c r="A600" s="31"/>
+      <c r="A600" s="34"/>
     </row>
     <row r="601">
-      <c r="A601" s="31"/>
+      <c r="A601" s="34"/>
     </row>
     <row r="602">
-      <c r="A602" s="31"/>
+      <c r="A602" s="34"/>
     </row>
     <row r="603">
-      <c r="A603" s="31"/>
+      <c r="A603" s="34"/>
     </row>
     <row r="604">
-      <c r="A604" s="31"/>
+      <c r="A604" s="34"/>
     </row>
     <row r="605">
-      <c r="A605" s="31"/>
+      <c r="A605" s="34"/>
     </row>
     <row r="606">
-      <c r="A606" s="31"/>
+      <c r="A606" s="34"/>
     </row>
     <row r="607">
-      <c r="A607" s="31"/>
+      <c r="A607" s="34"/>
     </row>
     <row r="608">
-      <c r="A608" s="31"/>
+      <c r="A608" s="34"/>
     </row>
     <row r="609">
-      <c r="A609" s="31"/>
+      <c r="A609" s="34"/>
     </row>
     <row r="610">
-      <c r="A610" s="31"/>
+      <c r="A610" s="34"/>
     </row>
     <row r="611">
-      <c r="A611" s="31"/>
+      <c r="A611" s="34"/>
     </row>
     <row r="612">
-      <c r="A612" s="31"/>
+      <c r="A612" s="34"/>
     </row>
     <row r="613">
-      <c r="A613" s="31"/>
+      <c r="A613" s="34"/>
     </row>
     <row r="614">
-      <c r="A614" s="31"/>
+      <c r="A614" s="34"/>
     </row>
     <row r="615">
-      <c r="A615" s="31"/>
+      <c r="A615" s="34"/>
     </row>
     <row r="616">
-      <c r="A616" s="31"/>
+      <c r="A616" s="34"/>
     </row>
     <row r="617">
-      <c r="A617" s="31"/>
+      <c r="A617" s="34"/>
     </row>
     <row r="618">
-      <c r="A618" s="31"/>
+      <c r="A618" s="34"/>
     </row>
     <row r="619">
-      <c r="A619" s="31"/>
+      <c r="A619" s="34"/>
     </row>
     <row r="620">
-      <c r="A620" s="31"/>
+      <c r="A620" s="34"/>
     </row>
     <row r="621">
-      <c r="A621" s="31"/>
+      <c r="A621" s="34"/>
     </row>
     <row r="622">
-      <c r="A622" s="31"/>
+      <c r="A622" s="34"/>
     </row>
     <row r="623">
-      <c r="A623" s="31"/>
+      <c r="A623" s="34"/>
     </row>
     <row r="624">
-      <c r="A624" s="31"/>
+      <c r="A624" s="34"/>
     </row>
     <row r="625">
-      <c r="A625" s="31"/>
+      <c r="A625" s="34"/>
     </row>
     <row r="626">
-      <c r="A626" s="31"/>
+      <c r="A626" s="34"/>
     </row>
     <row r="627">
-      <c r="A627" s="31"/>
+      <c r="A627" s="34"/>
     </row>
     <row r="628">
-      <c r="A628" s="31"/>
+      <c r="A628" s="34"/>
     </row>
     <row r="629">
-      <c r="A629" s="31"/>
+      <c r="A629" s="34"/>
     </row>
     <row r="630">
-      <c r="A630" s="31"/>
+      <c r="A630" s="34"/>
     </row>
     <row r="631">
-      <c r="A631" s="31"/>
+      <c r="A631" s="34"/>
     </row>
     <row r="632">
-      <c r="A632" s="31"/>
+      <c r="A632" s="34"/>
     </row>
     <row r="633">
-      <c r="A633" s="31"/>
+      <c r="A633" s="34"/>
     </row>
     <row r="634">
-      <c r="A634" s="31"/>
+      <c r="A634" s="34"/>
     </row>
     <row r="635">
-      <c r="A635" s="31"/>
+      <c r="A635" s="34"/>
     </row>
     <row r="636">
-      <c r="A636" s="31"/>
+      <c r="A636" s="34"/>
     </row>
     <row r="637">
-      <c r="A637" s="31"/>
+      <c r="A637" s="34"/>
     </row>
     <row r="638">
-      <c r="A638" s="31"/>
+      <c r="A638" s="34"/>
     </row>
     <row r="639">
-      <c r="A639" s="31"/>
+      <c r="A639" s="34"/>
     </row>
     <row r="640">
-      <c r="A640" s="31"/>
+      <c r="A640" s="34"/>
     </row>
     <row r="641">
-      <c r="A641" s="31"/>
+      <c r="A641" s="34"/>
     </row>
     <row r="642">
-      <c r="A642" s="31"/>
+      <c r="A642" s="34"/>
     </row>
     <row r="643">
-      <c r="A643" s="31"/>
+      <c r="A643" s="34"/>
     </row>
     <row r="644">
-      <c r="A644" s="31"/>
+      <c r="A644" s="34"/>
     </row>
     <row r="645">
-      <c r="A645" s="31"/>
+      <c r="A645" s="34"/>
     </row>
     <row r="646">
-      <c r="A646" s="31"/>
+      <c r="A646" s="34"/>
     </row>
     <row r="647">
-      <c r="A647" s="31"/>
+      <c r="A647" s="34"/>
     </row>
     <row r="648">
-      <c r="A648" s="31"/>
+      <c r="A648" s="34"/>
     </row>
     <row r="649">
-      <c r="A649" s="31"/>
+      <c r="A649" s="34"/>
     </row>
     <row r="650">
-      <c r="A650" s="31"/>
+      <c r="A650" s="34"/>
     </row>
     <row r="651">
-      <c r="A651" s="31"/>
+      <c r="A651" s="34"/>
     </row>
     <row r="652">
-      <c r="A652" s="31"/>
+      <c r="A652" s="34"/>
     </row>
     <row r="653">
-      <c r="A653" s="31"/>
+      <c r="A653" s="34"/>
     </row>
     <row r="654">
-      <c r="A654" s="31"/>
+      <c r="A654" s="34"/>
     </row>
     <row r="655">
-      <c r="A655" s="31"/>
+      <c r="A655" s="34"/>
     </row>
     <row r="656">
-      <c r="A656" s="31"/>
+      <c r="A656" s="34"/>
     </row>
     <row r="657">
-      <c r="A657" s="31"/>
+      <c r="A657" s="34"/>
     </row>
     <row r="658">
-      <c r="A658" s="31"/>
+      <c r="A658" s="34"/>
     </row>
     <row r="659">
-      <c r="A659" s="31"/>
+      <c r="A659" s="34"/>
     </row>
     <row r="660">
-      <c r="A660" s="31"/>
+      <c r="A660" s="34"/>
     </row>
     <row r="661">
-      <c r="A661" s="31"/>
+      <c r="A661" s="34"/>
     </row>
     <row r="662">
-      <c r="A662" s="31"/>
+      <c r="A662" s="34"/>
     </row>
     <row r="663">
-      <c r="A663" s="31"/>
+      <c r="A663" s="34"/>
     </row>
     <row r="664">
-      <c r="A664" s="31"/>
+      <c r="A664" s="34"/>
     </row>
     <row r="665">
-      <c r="A665" s="31"/>
+      <c r="A665" s="34"/>
     </row>
     <row r="666">
-      <c r="A666" s="31"/>
+      <c r="A666" s="34"/>
     </row>
     <row r="667">
-      <c r="A667" s="31"/>
+      <c r="A667" s="34"/>
     </row>
     <row r="668">
-      <c r="A668" s="31"/>
+      <c r="A668" s="34"/>
     </row>
     <row r="669">
-      <c r="A669" s="31"/>
+      <c r="A669" s="34"/>
     </row>
     <row r="670">
-      <c r="A670" s="31"/>
+      <c r="A670" s="34"/>
     </row>
     <row r="671">
-      <c r="A671" s="31"/>
+      <c r="A671" s="34"/>
     </row>
     <row r="672">
-      <c r="A672" s="31"/>
+      <c r="A672" s="34"/>
     </row>
     <row r="673">
-      <c r="A673" s="31"/>
+      <c r="A673" s="34"/>
     </row>
     <row r="674">
-      <c r="A674" s="31"/>
+      <c r="A674" s="34"/>
     </row>
     <row r="675">
-      <c r="A675" s="31"/>
+      <c r="A675" s="34"/>
     </row>
     <row r="676">
-      <c r="A676" s="31"/>
+      <c r="A676" s="34"/>
     </row>
     <row r="677">
-      <c r="A677" s="31"/>
+      <c r="A677" s="34"/>
     </row>
     <row r="678">
-      <c r="A678" s="31"/>
+      <c r="A678" s="34"/>
     </row>
     <row r="679">
-      <c r="A679" s="31"/>
+      <c r="A679" s="34"/>
     </row>
     <row r="680">
-      <c r="A680" s="31"/>
+      <c r="A680" s="34"/>
     </row>
     <row r="681">
-      <c r="A681" s="31"/>
+      <c r="A681" s="34"/>
     </row>
     <row r="682">
-      <c r="A682" s="31"/>
+      <c r="A682" s="34"/>
     </row>
     <row r="683">
-      <c r="A683" s="31"/>
+      <c r="A683" s="34"/>
     </row>
     <row r="684">
-      <c r="A684" s="31"/>
+      <c r="A684" s="34"/>
     </row>
     <row r="685">
-      <c r="A685" s="31"/>
+      <c r="A685" s="34"/>
     </row>
     <row r="686">
-      <c r="A686" s="31"/>
+      <c r="A686" s="34"/>
     </row>
     <row r="687">
-      <c r="A687" s="31"/>
+      <c r="A687" s="34"/>
     </row>
     <row r="688">
-      <c r="A688" s="31"/>
+      <c r="A688" s="34"/>
     </row>
     <row r="689">
-      <c r="A689" s="31"/>
+      <c r="A689" s="34"/>
     </row>
     <row r="690">
-      <c r="A690" s="31"/>
+      <c r="A690" s="34"/>
     </row>
     <row r="691">
-      <c r="A691" s="31"/>
+      <c r="A691" s="34"/>
     </row>
     <row r="692">
-      <c r="A692" s="31"/>
+      <c r="A692" s="34"/>
     </row>
     <row r="693">
-      <c r="A693" s="31"/>
+      <c r="A693" s="34"/>
     </row>
     <row r="694">
-      <c r="A694" s="31"/>
+      <c r="A694" s="34"/>
     </row>
     <row r="695">
-      <c r="A695" s="31"/>
+      <c r="A695" s="34"/>
     </row>
     <row r="696">
-      <c r="A696" s="31"/>
+      <c r="A696" s="34"/>
     </row>
     <row r="697">
-      <c r="A697" s="31"/>
+      <c r="A697" s="34"/>
     </row>
     <row r="698">
-      <c r="A698" s="31"/>
+      <c r="A698" s="34"/>
     </row>
     <row r="699">
-      <c r="A699" s="31"/>
+      <c r="A699" s="34"/>
     </row>
     <row r="700">
-      <c r="A700" s="31"/>
+      <c r="A700" s="34"/>
     </row>
     <row r="701">
-      <c r="A701" s="31"/>
+      <c r="A701" s="34"/>
     </row>
     <row r="702">
-      <c r="A702" s="31"/>
+      <c r="A702" s="34"/>
     </row>
     <row r="703">
-      <c r="A703" s="31"/>
+      <c r="A703" s="34"/>
     </row>
     <row r="704">
-      <c r="A704" s="31"/>
+      <c r="A704" s="34"/>
     </row>
     <row r="705">
-      <c r="A705" s="31"/>
+      <c r="A705" s="34"/>
     </row>
     <row r="706">
-      <c r="A706" s="31"/>
+      <c r="A706" s="34"/>
     </row>
     <row r="707">
-      <c r="A707" s="31"/>
+      <c r="A707" s="34"/>
     </row>
     <row r="708">
-      <c r="A708" s="31"/>
+      <c r="A708" s="34"/>
     </row>
     <row r="709">
-      <c r="A709" s="31"/>
+      <c r="A709" s="34"/>
     </row>
     <row r="710">
-      <c r="A710" s="31"/>
+      <c r="A710" s="34"/>
     </row>
     <row r="711">
-      <c r="A711" s="31"/>
+      <c r="A711" s="34"/>
     </row>
     <row r="712">
-      <c r="A712" s="31"/>
+      <c r="A712" s="34"/>
     </row>
     <row r="713">
-      <c r="A713" s="31"/>
+      <c r="A713" s="34"/>
     </row>
     <row r="714">
-      <c r="A714" s="31"/>
+      <c r="A714" s="34"/>
     </row>
     <row r="715">
-      <c r="A715" s="31"/>
+      <c r="A715" s="34"/>
     </row>
     <row r="716">
-      <c r="A716" s="31"/>
+      <c r="A716" s="34"/>
     </row>
     <row r="717">
-      <c r="A717" s="31"/>
+      <c r="A717" s="34"/>
     </row>
     <row r="718">
-      <c r="A718" s="31"/>
+      <c r="A718" s="34"/>
     </row>
     <row r="719">
-      <c r="A719" s="31"/>
+      <c r="A719" s="34"/>
     </row>
     <row r="720">
-      <c r="A720" s="31"/>
+      <c r="A720" s="34"/>
     </row>
     <row r="721">
-      <c r="A721" s="31"/>
+      <c r="A721" s="34"/>
     </row>
     <row r="722">
-      <c r="A722" s="31"/>
+      <c r="A722" s="34"/>
     </row>
     <row r="723">
-      <c r="A723" s="31"/>
+      <c r="A723" s="34"/>
     </row>
     <row r="724">
-      <c r="A724" s="31"/>
+      <c r="A724" s="34"/>
     </row>
     <row r="725">
-      <c r="A725" s="31"/>
+      <c r="A725" s="34"/>
     </row>
     <row r="726">
-      <c r="A726" s="31"/>
+      <c r="A726" s="34"/>
     </row>
     <row r="727">
-      <c r="A727" s="31"/>
+      <c r="A727" s="34"/>
     </row>
     <row r="728">
-      <c r="A728" s="31"/>
+      <c r="A728" s="34"/>
     </row>
     <row r="729">
-      <c r="A729" s="31"/>
+      <c r="A729" s="34"/>
     </row>
     <row r="730">
-      <c r="A730" s="31"/>
+      <c r="A730" s="34"/>
     </row>
     <row r="731">
-      <c r="A731" s="31"/>
+      <c r="A731" s="34"/>
     </row>
     <row r="732">
-      <c r="A732" s="31"/>
+      <c r="A732" s="34"/>
     </row>
     <row r="733">
-      <c r="A733" s="31"/>
+      <c r="A733" s="34"/>
     </row>
     <row r="734">
-      <c r="A734" s="31"/>
+      <c r="A734" s="34"/>
     </row>
     <row r="735">
-      <c r="A735" s="31"/>
+      <c r="A735" s="34"/>
     </row>
     <row r="736">
-      <c r="A736" s="31"/>
+      <c r="A736" s="34"/>
     </row>
     <row r="737">
-      <c r="A737" s="31"/>
+      <c r="A737" s="34"/>
     </row>
     <row r="738">
-      <c r="A738" s="31"/>
+      <c r="A738" s="34"/>
     </row>
     <row r="739">
-      <c r="A739" s="31"/>
+      <c r="A739" s="34"/>
     </row>
     <row r="740">
-      <c r="A740" s="31"/>
+      <c r="A740" s="34"/>
     </row>
     <row r="741">
-      <c r="A741" s="31"/>
+      <c r="A741" s="34"/>
     </row>
     <row r="742">
-      <c r="A742" s="31"/>
+      <c r="A742" s="34"/>
     </row>
     <row r="743">
-      <c r="A743" s="31"/>
+      <c r="A743" s="34"/>
     </row>
     <row r="744">
-      <c r="A744" s="31"/>
+      <c r="A744" s="34"/>
     </row>
     <row r="745">
-      <c r="A745" s="31"/>
+      <c r="A745" s="34"/>
     </row>
     <row r="746">
-      <c r="A746" s="31"/>
+      <c r="A746" s="34"/>
     </row>
     <row r="747">
-      <c r="A747" s="31"/>
+      <c r="A747" s="34"/>
     </row>
     <row r="748">
-      <c r="A748" s="31"/>
+      <c r="A748" s="34"/>
     </row>
     <row r="749">
-      <c r="A749" s="31"/>
+      <c r="A749" s="34"/>
     </row>
     <row r="750">
-      <c r="A750" s="31"/>
+      <c r="A750" s="34"/>
     </row>
     <row r="751">
-      <c r="A751" s="31"/>
+      <c r="A751" s="34"/>
     </row>
     <row r="752">
-      <c r="A752" s="31"/>
+      <c r="A752" s="34"/>
     </row>
     <row r="753">
-      <c r="A753" s="31"/>
+      <c r="A753" s="34"/>
     </row>
     <row r="754">
-      <c r="A754" s="31"/>
+      <c r="A754" s="34"/>
     </row>
     <row r="755">
-      <c r="A755" s="31"/>
+      <c r="A755" s="34"/>
     </row>
     <row r="756">
-      <c r="A756" s="31"/>
+      <c r="A756" s="34"/>
     </row>
     <row r="757">
-      <c r="A757" s="31"/>
+      <c r="A757" s="34"/>
     </row>
     <row r="758">
-      <c r="A758" s="31"/>
+      <c r="A758" s="34"/>
     </row>
     <row r="759">
-      <c r="A759" s="31"/>
+      <c r="A759" s="34"/>
     </row>
     <row r="760">
-      <c r="A760" s="31"/>
+      <c r="A760" s="34"/>
     </row>
     <row r="761">
-      <c r="A761" s="31"/>
+      <c r="A761" s="34"/>
     </row>
     <row r="762">
-      <c r="A762" s="31"/>
+      <c r="A762" s="34"/>
     </row>
     <row r="763">
-      <c r="A763" s="31"/>
+      <c r="A763" s="34"/>
     </row>
     <row r="764">
-      <c r="A764" s="31"/>
+      <c r="A764" s="34"/>
     </row>
     <row r="765">
-      <c r="A765" s="31"/>
+      <c r="A765" s="34"/>
     </row>
     <row r="766">
-      <c r="A766" s="31"/>
+      <c r="A766" s="34"/>
     </row>
     <row r="767">
-      <c r="A767" s="31"/>
+      <c r="A767" s="34"/>
     </row>
     <row r="768">
-      <c r="A768" s="31"/>
+      <c r="A768" s="34"/>
     </row>
     <row r="769">
-      <c r="A769" s="31"/>
+      <c r="A769" s="34"/>
     </row>
     <row r="770">
-      <c r="A770" s="31"/>
+      <c r="A770" s="34"/>
     </row>
     <row r="771">
-      <c r="A771" s="31"/>
+      <c r="A771" s="34"/>
     </row>
     <row r="772">
-      <c r="A772" s="31"/>
+      <c r="A772" s="34"/>
     </row>
     <row r="773">
-      <c r="A773" s="31"/>
+      <c r="A773" s="34"/>
     </row>
     <row r="774">
-      <c r="A774" s="31"/>
+      <c r="A774" s="34"/>
     </row>
     <row r="775">
-      <c r="A775" s="31"/>
+      <c r="A775" s="34"/>
     </row>
     <row r="776">
-      <c r="A776" s="31"/>
+      <c r="A776" s="34"/>
     </row>
     <row r="777">
-      <c r="A777" s="31"/>
+      <c r="A777" s="34"/>
     </row>
     <row r="778">
-      <c r="A778" s="31"/>
+      <c r="A778" s="34"/>
     </row>
     <row r="779">
-      <c r="A779" s="31"/>
+      <c r="A779" s="34"/>
     </row>
     <row r="780">
-      <c r="A780" s="31"/>
+      <c r="A780" s="34"/>
     </row>
     <row r="781">
-      <c r="A781" s="31"/>
+      <c r="A781" s="34"/>
     </row>
     <row r="782">
-      <c r="A782" s="31"/>
+      <c r="A782" s="34"/>
     </row>
     <row r="783">
-      <c r="A783" s="31"/>
+      <c r="A783" s="34"/>
     </row>
     <row r="784">
-      <c r="A784" s="31"/>
+      <c r="A784" s="34"/>
     </row>
     <row r="785">
-      <c r="A785" s="31"/>
+      <c r="A785" s="34"/>
     </row>
     <row r="786">
-      <c r="A786" s="31"/>
+      <c r="A786" s="34"/>
     </row>
     <row r="787">
-      <c r="A787" s="31"/>
+      <c r="A787" s="34"/>
     </row>
     <row r="788">
-      <c r="A788" s="31"/>
+      <c r="A788" s="34"/>
     </row>
     <row r="789">
-      <c r="A789" s="31"/>
+      <c r="A789" s="34"/>
     </row>
     <row r="790">
-      <c r="A790" s="31"/>
+      <c r="A790" s="34"/>
     </row>
     <row r="791">
-      <c r="A791" s="31"/>
+      <c r="A791" s="34"/>
     </row>
     <row r="792">
-      <c r="A792" s="31"/>
+      <c r="A792" s="34"/>
     </row>
     <row r="793">
-      <c r="A793" s="31"/>
+      <c r="A793" s="34"/>
     </row>
     <row r="794">
-      <c r="A794" s="31"/>
+      <c r="A794" s="34"/>
     </row>
     <row r="795">
-      <c r="A795" s="31"/>
+      <c r="A795" s="34"/>
     </row>
     <row r="796">
-      <c r="A796" s="31"/>
+      <c r="A796" s="34"/>
     </row>
     <row r="797">
-      <c r="A797" s="31"/>
+      <c r="A797" s="34"/>
     </row>
     <row r="798">
-      <c r="A798" s="31"/>
+      <c r="A798" s="34"/>
     </row>
     <row r="799">
-      <c r="A799" s="31"/>
+      <c r="A799" s="34"/>
     </row>
     <row r="800">
-      <c r="A800" s="31"/>
+      <c r="A800" s="34"/>
     </row>
     <row r="801">
-      <c r="A801" s="31"/>
+      <c r="A801" s="34"/>
     </row>
     <row r="802">
-      <c r="A802" s="31"/>
+      <c r="A802" s="34"/>
     </row>
     <row r="803">
-      <c r="A803" s="31"/>
+      <c r="A803" s="34"/>
     </row>
     <row r="804">
-      <c r="A804" s="31"/>
+      <c r="A804" s="34"/>
     </row>
     <row r="805">
-      <c r="A805" s="31"/>
+      <c r="A805" s="34"/>
     </row>
     <row r="806">
-      <c r="A806" s="31"/>
+      <c r="A806" s="34"/>
     </row>
     <row r="807">
-      <c r="A807" s="31"/>
+      <c r="A807" s="34"/>
     </row>
     <row r="808">
-      <c r="A808" s="31"/>
+      <c r="A808" s="34"/>
     </row>
     <row r="809">
-      <c r="A809" s="31"/>
+      <c r="A809" s="34"/>
     </row>
     <row r="810">
-      <c r="A810" s="31"/>
+      <c r="A810" s="34"/>
     </row>
     <row r="811">
-      <c r="A811" s="31"/>
+      <c r="A811" s="34"/>
     </row>
     <row r="812">
-      <c r="A812" s="31"/>
+      <c r="A812" s="34"/>
     </row>
     <row r="813">
-      <c r="A813" s="31"/>
+      <c r="A813" s="34"/>
     </row>
     <row r="814">
-      <c r="A814" s="31"/>
+      <c r="A814" s="34"/>
     </row>
     <row r="815">
-      <c r="A815" s="31"/>
+      <c r="A815" s="34"/>
     </row>
     <row r="816">
-      <c r="A816" s="31"/>
+      <c r="A816" s="34"/>
     </row>
     <row r="817">
-      <c r="A817" s="31"/>
+      <c r="A817" s="34"/>
     </row>
     <row r="818">
-      <c r="A818" s="31"/>
+      <c r="A818" s="34"/>
     </row>
     <row r="819">
-      <c r="A819" s="31"/>
+      <c r="A819" s="34"/>
     </row>
     <row r="820">
-      <c r="A820" s="31"/>
+      <c r="A820" s="34"/>
     </row>
     <row r="821">
-      <c r="A821" s="31"/>
+      <c r="A821" s="34"/>
     </row>
     <row r="822">
-      <c r="A822" s="31"/>
+      <c r="A822" s="34"/>
     </row>
     <row r="823">
-      <c r="A823" s="31"/>
+      <c r="A823" s="34"/>
     </row>
     <row r="824">
-      <c r="A824" s="31"/>
+      <c r="A824" s="34"/>
     </row>
     <row r="825">
-      <c r="A825" s="31"/>
+      <c r="A825" s="34"/>
     </row>
     <row r="826">
-      <c r="A826" s="31"/>
+      <c r="A826" s="34"/>
     </row>
     <row r="827">
-      <c r="A827" s="31"/>
+      <c r="A827" s="34"/>
     </row>
     <row r="828">
-      <c r="A828" s="31"/>
+      <c r="A828" s="34"/>
     </row>
     <row r="829">
-      <c r="A829" s="31"/>
+      <c r="A829" s="34"/>
     </row>
     <row r="830">
-      <c r="A830" s="31"/>
+      <c r="A830" s="34"/>
     </row>
     <row r="831">
-      <c r="A831" s="31"/>
+      <c r="A831" s="34"/>
     </row>
     <row r="832">
-      <c r="A832" s="31"/>
+      <c r="A832" s="34"/>
     </row>
     <row r="833">
-      <c r="A833" s="31"/>
+      <c r="A833" s="34"/>
     </row>
     <row r="834">
-      <c r="A834" s="31"/>
+      <c r="A834" s="34"/>
     </row>
     <row r="835">
-      <c r="A835" s="31"/>
+      <c r="A835" s="34"/>
     </row>
     <row r="836">
-      <c r="A836" s="31"/>
+      <c r="A836" s="34"/>
     </row>
     <row r="837">
-      <c r="A837" s="31"/>
+      <c r="A837" s="34"/>
     </row>
     <row r="838">
-      <c r="A838" s="31"/>
+      <c r="A838" s="34"/>
     </row>
     <row r="839">
-      <c r="A839" s="31"/>
+      <c r="A839" s="34"/>
     </row>
     <row r="840">
-      <c r="A840" s="31"/>
+      <c r="A840" s="34"/>
     </row>
     <row r="841">
-      <c r="A841" s="31"/>
+      <c r="A841" s="34"/>
     </row>
     <row r="842">
-      <c r="A842" s="31"/>
+      <c r="A842" s="34"/>
     </row>
     <row r="843">
-      <c r="A843" s="31"/>
+      <c r="A843" s="34"/>
     </row>
     <row r="844">
-      <c r="A844" s="31"/>
+      <c r="A844" s="34"/>
     </row>
     <row r="845">
-      <c r="A845" s="31"/>
+      <c r="A845" s="34"/>
     </row>
     <row r="846">
-      <c r="A846" s="31"/>
+      <c r="A846" s="34"/>
     </row>
     <row r="847">
-      <c r="A847" s="31"/>
+      <c r="A847" s="34"/>
     </row>
     <row r="848">
-      <c r="A848" s="31"/>
+      <c r="A848" s="34"/>
     </row>
     <row r="849">
-      <c r="A849" s="31"/>
+      <c r="A849" s="34"/>
     </row>
     <row r="850">
-      <c r="A850" s="31"/>
+      <c r="A850" s="34"/>
     </row>
     <row r="851">
-      <c r="A851" s="31"/>
+      <c r="A851" s="34"/>
     </row>
     <row r="852">
-      <c r="A852" s="31"/>
+      <c r="A852" s="34"/>
     </row>
     <row r="853">
-      <c r="A853" s="31"/>
+      <c r="A853" s="34"/>
     </row>
     <row r="854">
-      <c r="A854" s="31"/>
+      <c r="A854" s="34"/>
     </row>
     <row r="855">
-      <c r="A855" s="31"/>
+      <c r="A855" s="34"/>
     </row>
     <row r="856">
-      <c r="A856" s="31"/>
+      <c r="A856" s="34"/>
     </row>
     <row r="857">
-      <c r="A857" s="31"/>
+      <c r="A857" s="34"/>
     </row>
     <row r="858">
-      <c r="A858" s="31"/>
+      <c r="A858" s="34"/>
     </row>
     <row r="859">
-      <c r="A859" s="31"/>
+      <c r="A859" s="34"/>
     </row>
     <row r="860">
-      <c r="A860" s="31"/>
+      <c r="A860" s="34"/>
     </row>
     <row r="861">
-      <c r="A861" s="31"/>
+      <c r="A861" s="34"/>
     </row>
     <row r="862">
-      <c r="A862" s="31"/>
+      <c r="A862" s="34"/>
     </row>
     <row r="863">
-      <c r="A863" s="31"/>
+      <c r="A863" s="34"/>
     </row>
     <row r="864">
-      <c r="A864" s="31"/>
+      <c r="A864" s="34"/>
     </row>
     <row r="865">
-      <c r="A865" s="31"/>
+      <c r="A865" s="34"/>
     </row>
     <row r="866">
-      <c r="A866" s="31"/>
+      <c r="A866" s="34"/>
     </row>
     <row r="867">
-      <c r="A867" s="31"/>
+      <c r="A867" s="34"/>
     </row>
     <row r="868">
-      <c r="A868" s="31"/>
+      <c r="A868" s="34"/>
     </row>
     <row r="869">
-      <c r="A869" s="31"/>
+      <c r="A869" s="34"/>
     </row>
     <row r="870">
-      <c r="A870" s="31"/>
+      <c r="A870" s="34"/>
     </row>
     <row r="871">
-      <c r="A871" s="31"/>
+      <c r="A871" s="34"/>
     </row>
     <row r="872">
-      <c r="A872" s="31"/>
+      <c r="A872" s="34"/>
     </row>
     <row r="873">
-      <c r="A873" s="31"/>
+      <c r="A873" s="34"/>
     </row>
     <row r="874">
-      <c r="A874" s="31"/>
+      <c r="A874" s="34"/>
     </row>
     <row r="875">
-      <c r="A875" s="31"/>
+      <c r="A875" s="34"/>
     </row>
     <row r="876">
-      <c r="A876" s="31"/>
+      <c r="A876" s="34"/>
     </row>
     <row r="877">
-      <c r="A877" s="31"/>
+      <c r="A877" s="34"/>
     </row>
     <row r="878">
-      <c r="A878" s="31"/>
+      <c r="A878" s="34"/>
     </row>
     <row r="879">
-      <c r="A879" s="31"/>
+      <c r="A879" s="34"/>
     </row>
     <row r="880">
-      <c r="A880" s="31"/>
+      <c r="A880" s="34"/>
     </row>
     <row r="881">
-      <c r="A881" s="31"/>
+      <c r="A881" s="34"/>
     </row>
     <row r="882">
-      <c r="A882" s="31"/>
+      <c r="A882" s="34"/>
     </row>
     <row r="883">
-      <c r="A883" s="31"/>
+      <c r="A883" s="34"/>
     </row>
     <row r="884">
-      <c r="A884" s="31"/>
+      <c r="A884" s="34"/>
     </row>
     <row r="885">
-      <c r="A885" s="31"/>
+      <c r="A885" s="34"/>
     </row>
     <row r="886">
-      <c r="A886" s="31"/>
+      <c r="A886" s="34"/>
     </row>
     <row r="887">
-      <c r="A887" s="31"/>
+      <c r="A887" s="34"/>
     </row>
     <row r="888">
-      <c r="A888" s="31"/>
+      <c r="A888" s="34"/>
     </row>
     <row r="889">
-      <c r="A889" s="31"/>
+      <c r="A889" s="34"/>
     </row>
     <row r="890">
-      <c r="A890" s="31"/>
+      <c r="A890" s="34"/>
     </row>
     <row r="891">
-      <c r="A891" s="31"/>
+      <c r="A891" s="34"/>
     </row>
     <row r="892">
-      <c r="A892" s="31"/>
+      <c r="A892" s="34"/>
     </row>
     <row r="893">
-      <c r="A893" s="31"/>
+      <c r="A893" s="34"/>
     </row>
     <row r="894">
-      <c r="A894" s="31"/>
+      <c r="A894" s="34"/>
     </row>
     <row r="895">
-      <c r="A895" s="31"/>
+      <c r="A895" s="34"/>
     </row>
     <row r="896">
-      <c r="A896" s="31"/>
+      <c r="A896" s="34"/>
     </row>
     <row r="897">
-      <c r="A897" s="31"/>
+      <c r="A897" s="34"/>
     </row>
     <row r="898">
-      <c r="A898" s="31"/>
+      <c r="A898" s="34"/>
     </row>
     <row r="899">
-      <c r="A899" s="31"/>
+      <c r="A899" s="34"/>
     </row>
     <row r="900">
-      <c r="A900" s="31"/>
+      <c r="A900" s="34"/>
     </row>
     <row r="901">
-      <c r="A901" s="31"/>
+      <c r="A901" s="34"/>
     </row>
     <row r="902">
-      <c r="A902" s="31"/>
+      <c r="A902" s="34"/>
     </row>
     <row r="903">
-      <c r="A903" s="31"/>
+      <c r="A903" s="34"/>
     </row>
     <row r="904">
-      <c r="A904" s="31"/>
+      <c r="A904" s="34"/>
     </row>
     <row r="905">
-      <c r="A905" s="31"/>
+      <c r="A905" s="34"/>
     </row>
     <row r="906">
-      <c r="A906" s="31"/>
+      <c r="A906" s="34"/>
     </row>
     <row r="907">
-      <c r="A907" s="31"/>
+      <c r="A907" s="34"/>
     </row>
     <row r="908">
-      <c r="A908" s="31"/>
+      <c r="A908" s="34"/>
     </row>
     <row r="909">
-      <c r="A909" s="31"/>
+      <c r="A909" s="34"/>
     </row>
     <row r="910">
-      <c r="A910" s="31"/>
+      <c r="A910" s="34"/>
     </row>
     <row r="911">
-      <c r="A911" s="31"/>
+      <c r="A911" s="34"/>
     </row>
     <row r="912">
-      <c r="A912" s="31"/>
+      <c r="A912" s="34"/>
     </row>
     <row r="913">
-      <c r="A913" s="31"/>
+      <c r="A913" s="34"/>
     </row>
     <row r="914">
-      <c r="A914" s="31"/>
+      <c r="A914" s="34"/>
     </row>
     <row r="915">
-      <c r="A915" s="31"/>
+      <c r="A915" s="34"/>
     </row>
     <row r="916">
-      <c r="A916" s="31"/>
+      <c r="A916" s="34"/>
     </row>
     <row r="917">
-      <c r="A917" s="31"/>
+      <c r="A917" s="34"/>
     </row>
     <row r="918">
-      <c r="A918" s="31"/>
+      <c r="A918" s="34"/>
     </row>
     <row r="919">
-      <c r="A919" s="31"/>
+      <c r="A919" s="34"/>
     </row>
     <row r="920">
-      <c r="A920" s="31"/>
+      <c r="A920" s="34"/>
     </row>
     <row r="921">
-      <c r="A921" s="31"/>
+      <c r="A921" s="34"/>
     </row>
     <row r="922">
-      <c r="A922" s="31"/>
+      <c r="A922" s="34"/>
     </row>
     <row r="923">
-      <c r="A923" s="31"/>
+      <c r="A923" s="34"/>
     </row>
     <row r="924">
-      <c r="A924" s="31"/>
+      <c r="A924" s="34"/>
     </row>
     <row r="925">
-      <c r="A925" s="31"/>
+      <c r="A925" s="34"/>
     </row>
     <row r="926">
-      <c r="A926" s="31"/>
+      <c r="A926" s="34"/>
     </row>
     <row r="927">
-      <c r="A927" s="31"/>
+      <c r="A927" s="34"/>
     </row>
     <row r="928">
-      <c r="A928" s="31"/>
+      <c r="A928" s="34"/>
     </row>
     <row r="929">
-      <c r="A929" s="31"/>
+      <c r="A929" s="34"/>
     </row>
     <row r="930">
-      <c r="A930" s="31"/>
+      <c r="A930" s="34"/>
     </row>
     <row r="931">
-      <c r="A931" s="31"/>
+      <c r="A931" s="34"/>
     </row>
     <row r="932">
-      <c r="A932" s="31"/>
+      <c r="A932" s="34"/>
     </row>
     <row r="933">
-      <c r="A933" s="31"/>
+      <c r="A933" s="34"/>
     </row>
     <row r="934">
-      <c r="A934" s="31"/>
+      <c r="A934" s="34"/>
     </row>
     <row r="935">
-      <c r="A935" s="31"/>
+      <c r="A935" s="34"/>
     </row>
     <row r="936">
-      <c r="A936" s="31"/>
+      <c r="A936" s="34"/>
     </row>
     <row r="937">
-      <c r="A937" s="31"/>
+      <c r="A937" s="34"/>
     </row>
     <row r="938">
-      <c r="A938" s="31"/>
+      <c r="A938" s="34"/>
     </row>
     <row r="939">
-      <c r="A939" s="31"/>
+      <c r="A939" s="34"/>
     </row>
     <row r="940">
-      <c r="A940" s="31"/>
+      <c r="A940" s="34"/>
     </row>
     <row r="941">
-      <c r="A941" s="31"/>
+      <c r="A941" s="34"/>
     </row>
     <row r="942">
-      <c r="A942" s="31"/>
+      <c r="A942" s="34"/>
     </row>
     <row r="943">
-      <c r="A943" s="31"/>
+      <c r="A943" s="34"/>
     </row>
     <row r="944">
-      <c r="A944" s="31"/>
+      <c r="A944" s="34"/>
     </row>
     <row r="945">
-      <c r="A945" s="31"/>
+      <c r="A945" s="34"/>
     </row>
     <row r="946">
-      <c r="A946" s="31"/>
+      <c r="A946" s="34"/>
     </row>
     <row r="947">
-      <c r="A947" s="31"/>
+      <c r="A947" s="34"/>
     </row>
     <row r="948">
-      <c r="A948" s="31"/>
+      <c r="A948" s="34"/>
     </row>
     <row r="949">
-      <c r="A949" s="31"/>
+      <c r="A949" s="34"/>
     </row>
     <row r="950">
-      <c r="A950" s="31"/>
+      <c r="A950" s="34"/>
     </row>
     <row r="951">
-      <c r="A951" s="31"/>
+      <c r="A951" s="34"/>
     </row>
     <row r="952">
-      <c r="A952" s="31"/>
+      <c r="A952" s="34"/>
     </row>
     <row r="953">
-      <c r="A953" s="31"/>
+      <c r="A953" s="34"/>
     </row>
     <row r="954">
-      <c r="A954" s="31"/>
+      <c r="A954" s="34"/>
     </row>
     <row r="955">
-      <c r="A955" s="31"/>
+      <c r="A955" s="34"/>
     </row>
     <row r="956">
-      <c r="A956" s="31"/>
+      <c r="A956" s="34"/>
     </row>
     <row r="957">
-      <c r="A957" s="31"/>
+      <c r="A957" s="34"/>
     </row>
     <row r="958">
-      <c r="A958" s="31"/>
+      <c r="A958" s="34"/>
     </row>
     <row r="959">
-      <c r="A959" s="31"/>
+      <c r="A959" s="34"/>
     </row>
     <row r="960">
-      <c r="A960" s="31"/>
+      <c r="A960" s="34"/>
     </row>
     <row r="961">
-      <c r="A961" s="31"/>
+      <c r="A961" s="34"/>
     </row>
     <row r="962">
-      <c r="A962" s="31"/>
+      <c r="A962" s="34"/>
     </row>
     <row r="963">
-      <c r="A963" s="31"/>
+      <c r="A963" s="34"/>
     </row>
     <row r="964">
-      <c r="A964" s="31"/>
+      <c r="A964" s="34"/>
     </row>
     <row r="965">
-      <c r="A965" s="31"/>
+      <c r="A965" s="34"/>
     </row>
     <row r="966">
-      <c r="A966" s="31"/>
+      <c r="A966" s="34"/>
     </row>
     <row r="967">
-      <c r="A967" s="31"/>
+      <c r="A967" s="34"/>
     </row>
     <row r="968">
-      <c r="A968" s="31"/>
+      <c r="A968" s="34"/>
     </row>
     <row r="969">
-      <c r="A969" s="31"/>
+      <c r="A969" s="34"/>
     </row>
     <row r="970">
-      <c r="A970" s="31"/>
+      <c r="A970" s="34"/>
     </row>
     <row r="971">
-      <c r="A971" s="31"/>
+      <c r="A971" s="34"/>
     </row>
     <row r="972">
-      <c r="A972" s="31"/>
+      <c r="A972" s="34"/>
     </row>
     <row r="973">
-      <c r="A973" s="31"/>
+      <c r="A973" s="34"/>
     </row>
     <row r="974">
-      <c r="A974" s="31"/>
+      <c r="A974" s="34"/>
     </row>
     <row r="975">
-      <c r="A975" s="31"/>
+      <c r="A975" s="34"/>
     </row>
     <row r="976">
-      <c r="A976" s="31"/>
+      <c r="A976" s="34"/>
     </row>
     <row r="977">
-      <c r="A977" s="31"/>
+      <c r="A977" s="34"/>
     </row>
     <row r="978">
-      <c r="A978" s="31"/>
+      <c r="A978" s="34"/>
     </row>
     <row r="979">
-      <c r="A979" s="31"/>
+      <c r="A979" s="34"/>
     </row>
     <row r="980">
-      <c r="A980" s="31"/>
+      <c r="A980" s="34"/>
     </row>
     <row r="981">
-      <c r="A981" s="31"/>
+      <c r="A981" s="34"/>
     </row>
     <row r="982">
-      <c r="A982" s="31"/>
+      <c r="A982" s="34"/>
     </row>
     <row r="983">
-      <c r="A983" s="31"/>
+      <c r="A983" s="34"/>
     </row>
     <row r="984">
-      <c r="A984" s="31"/>
+      <c r="A984" s="34"/>
     </row>
     <row r="985">
-      <c r="A985" s="31"/>
+      <c r="A985" s="34"/>
     </row>
     <row r="986">
-      <c r="A986" s="31"/>
+      <c r="A986" s="34"/>
     </row>
     <row r="987">
-      <c r="A987" s="31"/>
+      <c r="A987" s="34"/>
     </row>
     <row r="988">
-      <c r="A988" s="31"/>
+      <c r="A988" s="34"/>
     </row>
     <row r="989">
-      <c r="A989" s="31"/>
+      <c r="A989" s="34"/>
     </row>
     <row r="990">
-      <c r="A990" s="31"/>
+      <c r="A990" s="34"/>
     </row>
     <row r="991">
-      <c r="A991" s="31"/>
+      <c r="A991" s="34"/>
     </row>
     <row r="992">
-      <c r="A992" s="31"/>
+      <c r="A992" s="34"/>
     </row>
     <row r="993">
-      <c r="A993" s="31"/>
+      <c r="A993" s="34"/>
     </row>
     <row r="994">
-      <c r="A994" s="31"/>
+      <c r="A994" s="34"/>
     </row>
     <row r="995">
-      <c r="A995" s="31"/>
+      <c r="A995" s="34"/>
     </row>
     <row r="996">
-      <c r="A996" s="31"/>
+      <c r="A996" s="34"/>
     </row>
     <row r="997">
-      <c r="A997" s="31"/>
+      <c r="A997" s="34"/>
     </row>
     <row r="998">
-      <c r="A998" s="31"/>
+      <c r="A998" s="34"/>
     </row>
     <row r="999">
-      <c r="A999" s="31"/>
+      <c r="A999" s="34"/>
     </row>
     <row r="1000">
-      <c r="A1000" s="31"/>
+      <c r="A1000" s="34"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G6:H6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2:E47 G7:H12">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:E47 G7:H12">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>